--- a/research/traditional_assets/database/data/malta/malta_retail_grocery_and_food.xlsx
+++ b/research/traditional_assets/database/data/malta/malta_retail_grocery_and_food.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07536390587509076</v>
+        <v>0.07512938220452794</v>
       </c>
       <c r="C2">
-        <v>227.4883164774228</v>
+        <v>226.2234041536253</v>
       </c>
       <c r="D2">
-        <v>226.0983164774228</v>
+        <v>227.1784041536253</v>
       </c>
       <c r="E2">
-        <v>-26.5</v>
+        <v>-24.155</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.345</v>
       </c>
       <c r="G2">
         <v>1.39</v>
@@ -1451,28 +1451,28 @@
         <v>20.4</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1179535</v>
       </c>
       <c r="N2">
-        <v>20.4</v>
+        <v>20.2820465</v>
       </c>
       <c r="O2">
-        <v>7.139999999999999</v>
+        <v>7.098716274999999</v>
       </c>
       <c r="P2">
-        <v>13.26</v>
+        <v>13.183330225</v>
       </c>
       <c r="Q2">
-        <v>16.16</v>
+        <v>16.083330225</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07536390587509076</v>
+        <v>0.075558012327806</v>
       </c>
       <c r="T2">
-        <v>0.5414733185171841</v>
+        <v>0.5450284463660343</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>172.9495097644411</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07512938220452794</v>
+        <v>0.07489485853396512</v>
       </c>
       <c r="C3">
-        <v>226.2234041536253</v>
+        <v>224.9688606732278</v>
       </c>
       <c r="D3">
-        <v>227.1784041536253</v>
+        <v>228.2688606732278</v>
       </c>
       <c r="E3">
-        <v>-24.155</v>
+        <v>-21.81</v>
       </c>
       <c r="F3">
-        <v>2.345</v>
+        <v>4.69</v>
       </c>
       <c r="G3">
         <v>1.39</v>
@@ -1533,28 +1533,28 @@
         <v>20.4</v>
       </c>
       <c r="M3">
-        <v>0.1179535</v>
+        <v>0.235907</v>
       </c>
       <c r="N3">
-        <v>20.2820465</v>
+        <v>20.164093</v>
       </c>
       <c r="O3">
-        <v>7.098716274999999</v>
+        <v>7.057432549999999</v>
       </c>
       <c r="P3">
-        <v>13.183330225</v>
+        <v>13.10666045</v>
       </c>
       <c r="Q3">
-        <v>16.083330225</v>
+        <v>16.00666045</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.075558012327806</v>
+        <v>0.0757560801366991</v>
       </c>
       <c r="T3">
-        <v>0.5450284463660343</v>
+        <v>0.5486561278444528</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>172.9495097644411</v>
+        <v>86.47475488222052</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07489485853396512</v>
+        <v>0.0746603348634023</v>
       </c>
       <c r="C4">
-        <v>224.9688606732278</v>
+        <v>223.7248360677511</v>
       </c>
       <c r="D4">
-        <v>228.2688606732278</v>
+        <v>229.3698360677511</v>
       </c>
       <c r="E4">
-        <v>-21.81</v>
+        <v>-19.465</v>
       </c>
       <c r="F4">
-        <v>4.69</v>
+        <v>7.035</v>
       </c>
       <c r="G4">
         <v>1.39</v>
@@ -1615,28 +1615,28 @@
         <v>20.4</v>
       </c>
       <c r="M4">
-        <v>0.235907</v>
+        <v>0.3538605</v>
       </c>
       <c r="N4">
-        <v>20.164093</v>
+        <v>20.0461395</v>
       </c>
       <c r="O4">
-        <v>7.057432549999999</v>
+        <v>7.016148824999999</v>
       </c>
       <c r="P4">
-        <v>13.10666045</v>
+        <v>13.029990675</v>
       </c>
       <c r="Q4">
-        <v>16.00666045</v>
+        <v>15.929990675</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.0757560801366991</v>
+        <v>0.07595823181794051</v>
       </c>
       <c r="T4">
-        <v>0.5486561278444528</v>
+        <v>0.5523586068791274</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>86.47475488222052</v>
+        <v>57.64983658814702</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0746603348634023</v>
+        <v>0.07442581119283947</v>
       </c>
       <c r="C5">
-        <v>223.7248360677511</v>
+        <v>222.491483277244</v>
       </c>
       <c r="D5">
-        <v>229.3698360677511</v>
+        <v>230.481483277244</v>
       </c>
       <c r="E5">
-        <v>-19.465</v>
+        <v>-17.12</v>
       </c>
       <c r="F5">
-        <v>7.035</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="G5">
         <v>1.39</v>
@@ -1697,28 +1697,28 @@
         <v>20.4</v>
       </c>
       <c r="M5">
-        <v>0.3538605</v>
+        <v>0.471814</v>
       </c>
       <c r="N5">
-        <v>20.0461395</v>
+        <v>19.928186</v>
       </c>
       <c r="O5">
-        <v>7.016148824999999</v>
+        <v>6.9748651</v>
       </c>
       <c r="P5">
-        <v>13.029990675</v>
+        <v>12.9533209</v>
       </c>
       <c r="Q5">
-        <v>15.929990675</v>
+        <v>15.8533209</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07595823181794051</v>
+        <v>0.07616459499254112</v>
       </c>
       <c r="T5">
-        <v>0.5523586068791274</v>
+        <v>0.5561382208936911</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>57.64983658814702</v>
+        <v>43.23737744111027</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07442581119283947</v>
+        <v>0.07419128752227666</v>
       </c>
       <c r="C6">
-        <v>222.491483277244</v>
+        <v>221.2689582211068</v>
       </c>
       <c r="D6">
-        <v>230.481483277244</v>
+        <v>231.6039582211068</v>
       </c>
       <c r="E6">
-        <v>-17.12</v>
+        <v>-14.775</v>
       </c>
       <c r="F6">
-        <v>9.380000000000001</v>
+        <v>11.725</v>
       </c>
       <c r="G6">
         <v>1.39</v>
@@ -1779,28 +1779,28 @@
         <v>20.4</v>
       </c>
       <c r="M6">
-        <v>0.471814</v>
+        <v>0.5897675</v>
       </c>
       <c r="N6">
-        <v>19.928186</v>
+        <v>19.8102325</v>
       </c>
       <c r="O6">
-        <v>6.9748651</v>
+        <v>6.933581374999999</v>
       </c>
       <c r="P6">
-        <v>12.9533209</v>
+        <v>12.876651125</v>
       </c>
       <c r="Q6">
-        <v>15.8533209</v>
+        <v>15.776651125</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07616459499254112</v>
+        <v>0.07637530265502807</v>
       </c>
       <c r="T6">
-        <v>0.5561382208936911</v>
+        <v>0.559997405729614</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>43.23737744111027</v>
+        <v>34.58990195288821</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07419128752227666</v>
+        <v>0.07395676385171383</v>
       </c>
       <c r="C7">
-        <v>221.2689582211068</v>
+        <v>220.0574198709967</v>
       </c>
       <c r="D7">
-        <v>231.6039582211068</v>
+        <v>232.7374198709967</v>
       </c>
       <c r="E7">
-        <v>-14.775</v>
+        <v>-12.43</v>
       </c>
       <c r="F7">
-        <v>11.725</v>
+        <v>14.07</v>
       </c>
       <c r="G7">
         <v>1.39</v>
@@ -1861,28 +1861,28 @@
         <v>20.4</v>
       </c>
       <c r="M7">
-        <v>0.5897675</v>
+        <v>0.7077209999999999</v>
       </c>
       <c r="N7">
-        <v>19.8102325</v>
+        <v>19.692279</v>
       </c>
       <c r="O7">
-        <v>6.933581374999999</v>
+        <v>6.89229765</v>
       </c>
       <c r="P7">
-        <v>12.876651125</v>
+        <v>12.79998135</v>
       </c>
       <c r="Q7">
-        <v>15.776651125</v>
+        <v>15.69998135</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07637530265502807</v>
+        <v>0.07659049345927005</v>
       </c>
       <c r="T7">
-        <v>0.559997405729614</v>
+        <v>0.5639387008811949</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>34.58990195288821</v>
+        <v>28.82491829407351</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07395676385171383</v>
+        <v>0.07372224018115103</v>
       </c>
       <c r="C8">
-        <v>220.0574198709967</v>
+        <v>218.8570303258821</v>
       </c>
       <c r="D8">
-        <v>232.7374198709967</v>
+        <v>233.8820303258821</v>
       </c>
       <c r="E8">
-        <v>-12.43</v>
+        <v>-10.085</v>
       </c>
       <c r="F8">
-        <v>14.07</v>
+        <v>16.415</v>
       </c>
       <c r="G8">
         <v>1.39</v>
@@ -1943,28 +1943,28 @@
         <v>20.4</v>
       </c>
       <c r="M8">
-        <v>0.7077209999999999</v>
+        <v>0.8256744999999999</v>
       </c>
       <c r="N8">
-        <v>19.692279</v>
+        <v>19.5743255</v>
       </c>
       <c r="O8">
-        <v>6.89229765</v>
+        <v>6.851013925</v>
       </c>
       <c r="P8">
-        <v>12.79998135</v>
+        <v>12.723311575</v>
       </c>
       <c r="Q8">
-        <v>15.69998135</v>
+        <v>15.623311575</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07659049345927005</v>
+        <v>0.07681031202274304</v>
       </c>
       <c r="T8">
-        <v>0.5639387008811949</v>
+        <v>0.5679647550682936</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>28.82491829407351</v>
+        <v>24.70707282349159</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07372224018115102</v>
+        <v>0.07348771651058821</v>
       </c>
       <c r="C9">
-        <v>218.8570303258822</v>
+        <v>217.6679548893252</v>
       </c>
       <c r="D9">
-        <v>233.8820303258822</v>
+        <v>235.0379548893252</v>
       </c>
       <c r="E9">
-        <v>-10.085</v>
+        <v>-7.739999999999998</v>
       </c>
       <c r="F9">
-        <v>16.415</v>
+        <v>18.76</v>
       </c>
       <c r="G9">
         <v>1.39</v>
@@ -2025,28 +2025,28 @@
         <v>20.4</v>
       </c>
       <c r="M9">
-        <v>0.8256745000000001</v>
+        <v>0.943628</v>
       </c>
       <c r="N9">
-        <v>19.5743255</v>
+        <v>19.456372</v>
       </c>
       <c r="O9">
-        <v>6.851013924999998</v>
+        <v>6.809730199999999</v>
       </c>
       <c r="P9">
-        <v>12.723311575</v>
+        <v>12.6466418</v>
       </c>
       <c r="Q9">
-        <v>15.623311575</v>
+        <v>15.5466418</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07681031202274304</v>
+        <v>0.07703490925063936</v>
       </c>
       <c r="T9">
-        <v>0.5679647550682936</v>
+        <v>0.5720783321725031</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>24.70707282349158</v>
+        <v>21.61868872055513</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07348771651058821</v>
+        <v>0.07325319284002539</v>
       </c>
       <c r="C10">
-        <v>217.6679548893252</v>
+        <v>216.4903621490647</v>
       </c>
       <c r="D10">
-        <v>235.0379548893252</v>
+        <v>236.2053621490647</v>
       </c>
       <c r="E10">
-        <v>-7.739999999999998</v>
+        <v>-5.395</v>
       </c>
       <c r="F10">
-        <v>18.76</v>
+        <v>21.105</v>
       </c>
       <c r="G10">
         <v>1.39</v>
@@ -2107,28 +2107,28 @@
         <v>20.4</v>
       </c>
       <c r="M10">
-        <v>0.943628</v>
+        <v>1.0615815</v>
       </c>
       <c r="N10">
-        <v>19.456372</v>
+        <v>19.3384185</v>
       </c>
       <c r="O10">
-        <v>6.809730199999999</v>
+        <v>6.768446474999999</v>
       </c>
       <c r="P10">
-        <v>12.6466418</v>
+        <v>12.569972025</v>
       </c>
       <c r="Q10">
-        <v>15.5466418</v>
+        <v>15.469972025</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07703490925063936</v>
+        <v>0.07726444268134658</v>
       </c>
       <c r="T10">
-        <v>0.5720783321725031</v>
+        <v>0.5762823175647173</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>21.61868872055513</v>
+        <v>19.21661219604901</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07325319284002539</v>
+        <v>0.07301866916946256</v>
       </c>
       <c r="C11">
-        <v>216.4903621490647</v>
+        <v>215.324424058985</v>
       </c>
       <c r="D11">
-        <v>236.2053621490647</v>
+        <v>237.384424058985</v>
       </c>
       <c r="E11">
-        <v>-5.395</v>
+        <v>-3.050000000000001</v>
       </c>
       <c r="F11">
-        <v>21.105</v>
+        <v>23.45</v>
       </c>
       <c r="G11">
         <v>1.39</v>
@@ -2189,28 +2189,28 @@
         <v>20.4</v>
       </c>
       <c r="M11">
-        <v>1.0615815</v>
+        <v>1.179535</v>
       </c>
       <c r="N11">
-        <v>19.3384185</v>
+        <v>19.220465</v>
       </c>
       <c r="O11">
-        <v>6.768446474999999</v>
+        <v>6.727162749999999</v>
       </c>
       <c r="P11">
-        <v>12.569972025</v>
+        <v>12.49330225</v>
       </c>
       <c r="Q11">
-        <v>15.469972025</v>
+        <v>15.39330225</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07726444268134658</v>
+        <v>0.07749907685495841</v>
       </c>
       <c r="T11">
-        <v>0.5762823175647173</v>
+        <v>0.5805797248545362</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>19.21661219604901</v>
+        <v>17.29495097644411</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07301866916946256</v>
+        <v>0.07278414549889975</v>
       </c>
       <c r="C12">
-        <v>215.324424058985</v>
+        <v>214.1703160235502</v>
       </c>
       <c r="D12">
-        <v>237.384424058985</v>
+        <v>238.5753160235502</v>
       </c>
       <c r="E12">
-        <v>-3.049999999999997</v>
+        <v>-0.7049999999999983</v>
       </c>
       <c r="F12">
-        <v>23.45</v>
+        <v>25.795</v>
       </c>
       <c r="G12">
         <v>1.39</v>
@@ -2271,28 +2271,28 @@
         <v>20.4</v>
       </c>
       <c r="M12">
-        <v>1.179535</v>
+        <v>1.2974885</v>
       </c>
       <c r="N12">
-        <v>19.220465</v>
+        <v>19.1025115</v>
       </c>
       <c r="O12">
-        <v>6.727162749999999</v>
+        <v>6.685879024999999</v>
       </c>
       <c r="P12">
-        <v>12.49330225</v>
+        <v>12.416632475</v>
       </c>
       <c r="Q12">
-        <v>15.39330225</v>
+        <v>15.316632475</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07749907685495841</v>
+        <v>0.07773898370662893</v>
       </c>
       <c r="T12">
-        <v>0.5805797248545362</v>
+        <v>0.5849737030946882</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>17.29495097644411</v>
+        <v>15.72268270585828</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07278414549889975</v>
+        <v>0.07254962182833694</v>
       </c>
       <c r="C13">
-        <v>214.1703160235502</v>
+        <v>213.0282169847945</v>
       </c>
       <c r="D13">
-        <v>238.5753160235502</v>
+        <v>239.7782169847945</v>
       </c>
       <c r="E13">
-        <v>-0.7049999999999983</v>
+        <v>1.640000000000001</v>
       </c>
       <c r="F13">
-        <v>25.795</v>
+        <v>28.14</v>
       </c>
       <c r="G13">
         <v>1.39</v>
@@ -2353,28 +2353,28 @@
         <v>20.4</v>
       </c>
       <c r="M13">
-        <v>1.2974885</v>
+        <v>1.415442</v>
       </c>
       <c r="N13">
-        <v>19.1025115</v>
+        <v>18.984558</v>
       </c>
       <c r="O13">
-        <v>6.685879024999999</v>
+        <v>6.6445953</v>
       </c>
       <c r="P13">
-        <v>12.416632475</v>
+        <v>12.3399627</v>
       </c>
       <c r="Q13">
-        <v>15.316632475</v>
+        <v>15.2399627</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07773898370662893</v>
+        <v>0.07798434298674653</v>
       </c>
       <c r="T13">
-        <v>0.5849737030946882</v>
+        <v>0.5894675444766617</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.72268270585828</v>
+        <v>14.41245914703676</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07254962182833694</v>
+        <v>0.07231509815777412</v>
       </c>
       <c r="C14">
-        <v>213.0282169847945</v>
+        <v>211.8983095119559</v>
       </c>
       <c r="D14">
-        <v>239.7782169847945</v>
+        <v>240.9933095119559</v>
       </c>
       <c r="E14">
-        <v>1.640000000000001</v>
+        <v>3.984999999999999</v>
       </c>
       <c r="F14">
-        <v>28.14</v>
+        <v>30.485</v>
       </c>
       <c r="G14">
         <v>1.39</v>
@@ -2435,28 +2435,28 @@
         <v>20.4</v>
       </c>
       <c r="M14">
-        <v>1.415442</v>
+        <v>1.5333955</v>
       </c>
       <c r="N14">
-        <v>18.984558</v>
+        <v>18.8666045</v>
       </c>
       <c r="O14">
-        <v>6.6445953</v>
+        <v>6.603311574999998</v>
       </c>
       <c r="P14">
-        <v>12.3399627</v>
+        <v>12.263292925</v>
       </c>
       <c r="Q14">
-        <v>15.2399627</v>
+        <v>15.163292925</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07798434298674653</v>
+        <v>0.0782353427100852</v>
       </c>
       <c r="T14">
-        <v>0.5894675444766617</v>
+        <v>0.5940646925570714</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.41245914703676</v>
+        <v>13.30380844341854</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07231509815777412</v>
+        <v>0.07221707448721131</v>
       </c>
       <c r="C15">
-        <v>211.8983095119559</v>
+        <v>210.0648378955756</v>
       </c>
       <c r="D15">
-        <v>240.9933095119559</v>
+        <v>241.5048378955756</v>
       </c>
       <c r="E15">
-        <v>3.984999999999999</v>
+        <v>6.330000000000005</v>
       </c>
       <c r="F15">
-        <v>30.485</v>
+        <v>32.83000000000001</v>
       </c>
       <c r="G15">
         <v>1.39</v>
@@ -2517,45 +2517,45 @@
         <v>20.4</v>
       </c>
       <c r="M15">
-        <v>1.5333955</v>
+        <v>1.700594</v>
       </c>
       <c r="N15">
-        <v>18.8666045</v>
+        <v>18.699406</v>
       </c>
       <c r="O15">
-        <v>6.603311574999998</v>
+        <v>6.5447921</v>
       </c>
       <c r="P15">
-        <v>12.263292925</v>
+        <v>12.1546139</v>
       </c>
       <c r="Q15">
-        <v>15.163292925</v>
+        <v>15.0546139</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0782353427100852</v>
+        <v>0.07849217963629221</v>
       </c>
       <c r="T15">
-        <v>0.5940646925570714</v>
+        <v>0.5987687510579559</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.35</v>
       </c>
       <c r="W15">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>13.30380844341854</v>
+        <v>11.99580852337477</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07221707448721131</v>
+        <v>0.07199230081664849</v>
       </c>
       <c r="C16">
-        <v>210.0648378955756</v>
+        <v>208.9010394831466</v>
       </c>
       <c r="D16">
-        <v>241.5048378955756</v>
+        <v>242.6860394831466</v>
       </c>
       <c r="E16">
-        <v>6.330000000000005</v>
+        <v>8.675000000000004</v>
       </c>
       <c r="F16">
-        <v>32.83000000000001</v>
+        <v>35.175</v>
       </c>
       <c r="G16">
         <v>1.39</v>
@@ -2599,28 +2599,28 @@
         <v>20.4</v>
       </c>
       <c r="M16">
-        <v>1.700594</v>
+        <v>1.822065</v>
       </c>
       <c r="N16">
-        <v>18.699406</v>
+        <v>18.577935</v>
       </c>
       <c r="O16">
-        <v>6.5447921</v>
+        <v>6.502277249999999</v>
       </c>
       <c r="P16">
-        <v>12.1546139</v>
+        <v>12.07565775</v>
       </c>
       <c r="Q16">
-        <v>15.0546139</v>
+        <v>14.97565775</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07849217963629221</v>
+        <v>0.07875505978429234</v>
       </c>
       <c r="T16">
-        <v>0.5987687510579559</v>
+        <v>0.6035834932882729</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.99580852337477</v>
+        <v>11.19608795514979</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07199230081664849</v>
+        <v>0.07176752714608567</v>
       </c>
       <c r="C17">
-        <v>208.9010394831466</v>
+        <v>207.7488523896201</v>
       </c>
       <c r="D17">
-        <v>242.6860394831466</v>
+        <v>243.8788523896201</v>
       </c>
       <c r="E17">
-        <v>8.674999999999997</v>
+        <v>11.02</v>
       </c>
       <c r="F17">
-        <v>35.175</v>
+        <v>37.52</v>
       </c>
       <c r="G17">
         <v>1.39</v>
@@ -2681,28 +2681,28 @@
         <v>20.4</v>
       </c>
       <c r="M17">
-        <v>1.822065</v>
+        <v>1.943536</v>
       </c>
       <c r="N17">
-        <v>18.577935</v>
+        <v>18.456464</v>
       </c>
       <c r="O17">
-        <v>6.50227725</v>
+        <v>6.459762399999999</v>
       </c>
       <c r="P17">
-        <v>12.07565775</v>
+        <v>11.9967016</v>
       </c>
       <c r="Q17">
-        <v>14.97565775</v>
+        <v>14.8967016</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07875505978429234</v>
+        <v>0.07902419898343532</v>
       </c>
       <c r="T17">
-        <v>0.6035834932882729</v>
+        <v>0.6085128722383593</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.19608795514979</v>
+        <v>10.49633245795292</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07176752714608567</v>
+        <v>0.07154275347552284</v>
       </c>
       <c r="C18">
-        <v>207.7488523896201</v>
+        <v>206.6084486711391</v>
       </c>
       <c r="D18">
-        <v>243.8788523896201</v>
+        <v>245.0834486711391</v>
       </c>
       <c r="E18">
-        <v>11.02</v>
+        <v>13.365</v>
       </c>
       <c r="F18">
-        <v>37.52</v>
+        <v>39.865</v>
       </c>
       <c r="G18">
         <v>1.39</v>
@@ -2763,28 +2763,28 @@
         <v>20.4</v>
       </c>
       <c r="M18">
-        <v>1.943536</v>
+        <v>2.065007</v>
       </c>
       <c r="N18">
-        <v>18.456464</v>
+        <v>18.334993</v>
       </c>
       <c r="O18">
-        <v>6.459762399999999</v>
+        <v>6.417247549999999</v>
       </c>
       <c r="P18">
-        <v>11.9967016</v>
+        <v>11.91774545</v>
       </c>
       <c r="Q18">
-        <v>14.8967016</v>
+        <v>14.81774545</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07902419898343532</v>
+        <v>0.07929982346448536</v>
       </c>
       <c r="T18">
-        <v>0.6085128722383593</v>
+        <v>0.6135610314041104</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>10.49633245795292</v>
+        <v>9.878901136896872</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07154275347552284</v>
+        <v>0.07151687980496003</v>
       </c>
       <c r="C19">
-        <v>206.6084486711391</v>
+        <v>204.402873769523</v>
       </c>
       <c r="D19">
-        <v>245.0834486711391</v>
+        <v>245.222873769523</v>
       </c>
       <c r="E19">
-        <v>13.365</v>
+        <v>15.71000000000001</v>
       </c>
       <c r="F19">
-        <v>39.865</v>
+        <v>42.21000000000001</v>
       </c>
       <c r="G19">
         <v>1.39</v>
@@ -2845,45 +2845,45 @@
         <v>20.4</v>
       </c>
       <c r="M19">
-        <v>2.065007</v>
+        <v>2.258235</v>
       </c>
       <c r="N19">
-        <v>18.334993</v>
+        <v>18.141765</v>
       </c>
       <c r="O19">
-        <v>6.417247549999999</v>
+        <v>6.349617749999999</v>
       </c>
       <c r="P19">
-        <v>11.91774545</v>
+        <v>11.79214725</v>
       </c>
       <c r="Q19">
-        <v>14.81774545</v>
+        <v>14.69214725</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07929982346448536</v>
+        <v>0.0795821704938537</v>
       </c>
       <c r="T19">
-        <v>0.6135610314041104</v>
+        <v>0.6187323164031725</v>
       </c>
       <c r="U19">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V19">
         <v>0.35</v>
       </c>
       <c r="W19">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>9.878901136896872</v>
+        <v>9.033603677208083</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07151687980496003</v>
+        <v>0.07130315613439722</v>
       </c>
       <c r="C20">
-        <v>204.402873769523</v>
+        <v>203.2156594400662</v>
       </c>
       <c r="D20">
-        <v>245.222873769523</v>
+        <v>246.3806594400662</v>
       </c>
       <c r="E20">
-        <v>15.71</v>
+        <v>18.055</v>
       </c>
       <c r="F20">
-        <v>42.21</v>
+        <v>44.555</v>
       </c>
       <c r="G20">
         <v>1.39</v>
@@ -2927,28 +2927,28 @@
         <v>20.4</v>
       </c>
       <c r="M20">
-        <v>2.258235</v>
+        <v>2.3836925</v>
       </c>
       <c r="N20">
-        <v>18.141765</v>
+        <v>18.0163075</v>
       </c>
       <c r="O20">
-        <v>6.349617749999999</v>
+        <v>6.305707624999999</v>
       </c>
       <c r="P20">
-        <v>11.79214725</v>
+        <v>11.710599875</v>
       </c>
       <c r="Q20">
-        <v>14.69214725</v>
+        <v>14.610599875</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.0795821704938537</v>
+        <v>0.07987148905481138</v>
       </c>
       <c r="T20">
-        <v>0.6187323164031725</v>
+        <v>0.6240312874515943</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.033603677208085</v>
+        <v>8.55815085209187</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07130315613439722</v>
+        <v>0.07108943246383441</v>
       </c>
       <c r="C21">
-        <v>203.2156594400662</v>
+        <v>202.039429620269</v>
       </c>
       <c r="D21">
-        <v>246.3806594400662</v>
+        <v>247.5494296202691</v>
       </c>
       <c r="E21">
-        <v>18.055</v>
+        <v>20.40000000000001</v>
       </c>
       <c r="F21">
-        <v>44.555</v>
+        <v>46.90000000000001</v>
       </c>
       <c r="G21">
         <v>1.39</v>
@@ -3009,28 +3009,28 @@
         <v>20.4</v>
       </c>
       <c r="M21">
-        <v>2.3836925</v>
+        <v>2.50915</v>
       </c>
       <c r="N21">
-        <v>18.0163075</v>
+        <v>17.89085</v>
       </c>
       <c r="O21">
-        <v>6.305707624999999</v>
+        <v>6.261797499999998</v>
       </c>
       <c r="P21">
-        <v>11.710599875</v>
+        <v>11.6290525</v>
       </c>
       <c r="Q21">
-        <v>14.610599875</v>
+        <v>14.5290525</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07987148905481138</v>
+        <v>0.080168040579793</v>
       </c>
       <c r="T21">
-        <v>0.6240312874515943</v>
+        <v>0.6294627327762266</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.55815085209187</v>
+        <v>8.130243309487273</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07108943246383441</v>
+        <v>0.07087570879327158</v>
       </c>
       <c r="C22">
-        <v>202.039429620269</v>
+        <v>200.8743413787883</v>
       </c>
       <c r="D22">
-        <v>247.5494296202691</v>
+        <v>248.7293413787883</v>
       </c>
       <c r="E22">
-        <v>20.40000000000001</v>
+        <v>22.745</v>
       </c>
       <c r="F22">
-        <v>46.90000000000001</v>
+        <v>49.245</v>
       </c>
       <c r="G22">
         <v>1.39</v>
@@ -3091,28 +3091,28 @@
         <v>20.4</v>
       </c>
       <c r="M22">
-        <v>2.50915</v>
+        <v>2.6346075</v>
       </c>
       <c r="N22">
-        <v>17.89085</v>
+        <v>17.7653925</v>
       </c>
       <c r="O22">
-        <v>6.261797499999998</v>
+        <v>6.217887374999998</v>
       </c>
       <c r="P22">
-        <v>11.6290525</v>
+        <v>11.547505125</v>
       </c>
       <c r="Q22">
-        <v>14.5290525</v>
+        <v>14.447505125</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.080168040579793</v>
+        <v>0.08047209973831845</v>
       </c>
       <c r="T22">
-        <v>0.6294627327762266</v>
+        <v>0.6350316830457862</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.130243309487273</v>
+        <v>7.743088866178358</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07087570879327158</v>
+        <v>0.07077638512270877</v>
       </c>
       <c r="C23">
-        <v>200.8743413787883</v>
+        <v>199.0815177468171</v>
       </c>
       <c r="D23">
-        <v>248.7293413787883</v>
+        <v>249.2815177468171</v>
       </c>
       <c r="E23">
-        <v>22.745</v>
+        <v>25.09</v>
       </c>
       <c r="F23">
-        <v>49.245</v>
+        <v>51.59</v>
       </c>
       <c r="G23">
         <v>1.39</v>
@@ -3173,45 +3173,45 @@
         <v>20.4</v>
       </c>
       <c r="M23">
-        <v>2.6346075</v>
+        <v>2.801337</v>
       </c>
       <c r="N23">
-        <v>17.7653925</v>
+        <v>17.598663</v>
       </c>
       <c r="O23">
-        <v>6.217887374999998</v>
+        <v>6.159532049999999</v>
       </c>
       <c r="P23">
-        <v>11.547505125</v>
+        <v>11.43913095</v>
       </c>
       <c r="Q23">
-        <v>14.447505125</v>
+        <v>14.33913095</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08047209973831845</v>
+        <v>0.08078395528552405</v>
       </c>
       <c r="T23">
-        <v>0.6350316830457862</v>
+        <v>0.6407434269120011</v>
       </c>
       <c r="U23">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V23">
         <v>0.35</v>
       </c>
       <c r="W23">
-        <v>0.034775</v>
+        <v>0.035295</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y23">
-        <v>7.743088866178358</v>
+        <v>7.28223701753841</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07077638512270877</v>
+        <v>0.07056786145214594</v>
       </c>
       <c r="C24">
-        <v>199.0815177468171</v>
+        <v>197.9037904640104</v>
       </c>
       <c r="D24">
-        <v>249.2815177468171</v>
+        <v>250.4487904640104</v>
       </c>
       <c r="E24">
-        <v>25.09</v>
+        <v>27.435</v>
       </c>
       <c r="F24">
-        <v>51.59</v>
+        <v>53.935</v>
       </c>
       <c r="G24">
         <v>1.39</v>
@@ -3255,28 +3255,28 @@
         <v>20.4</v>
       </c>
       <c r="M24">
-        <v>2.801337</v>
+        <v>2.9286705</v>
       </c>
       <c r="N24">
-        <v>17.598663</v>
+        <v>17.4713295</v>
       </c>
       <c r="O24">
-        <v>6.159532049999999</v>
+        <v>6.114965324999999</v>
       </c>
       <c r="P24">
-        <v>11.43913095</v>
+        <v>11.356364175</v>
       </c>
       <c r="Q24">
-        <v>14.33913095</v>
+        <v>14.256364175</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08078395528552405</v>
+        <v>0.08110391097681291</v>
       </c>
       <c r="T24">
-        <v>0.6407434269120011</v>
+        <v>0.6466035277617542</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.28223701753841</v>
+        <v>6.965618016775871</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07056786145214594</v>
+        <v>0.07035933778158313</v>
       </c>
       <c r="C25">
-        <v>197.9037904640104</v>
+        <v>196.7370462313397</v>
       </c>
       <c r="D25">
-        <v>250.4487904640104</v>
+        <v>251.6270462313397</v>
       </c>
       <c r="E25">
-        <v>27.435</v>
+        <v>29.78</v>
       </c>
       <c r="F25">
-        <v>53.935</v>
+        <v>56.28</v>
       </c>
       <c r="G25">
         <v>1.39</v>
@@ -3337,28 +3337,28 @@
         <v>20.4</v>
       </c>
       <c r="M25">
-        <v>2.9286705</v>
+        <v>3.056004</v>
       </c>
       <c r="N25">
-        <v>17.4713295</v>
+        <v>17.343996</v>
       </c>
       <c r="O25">
-        <v>6.114965324999999</v>
+        <v>6.070398599999999</v>
       </c>
       <c r="P25">
-        <v>11.356364175</v>
+        <v>11.2735974</v>
       </c>
       <c r="Q25">
-        <v>14.256364175</v>
+        <v>14.1735974</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08110391097681291</v>
+        <v>0.08143228655471464</v>
       </c>
       <c r="T25">
-        <v>0.6466035277617542</v>
+        <v>0.652617841791764</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.965618016775871</v>
+        <v>6.675383932743542</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07035933778158313</v>
+        <v>0.07015081411102032</v>
       </c>
       <c r="C26">
-        <v>196.7370462313397</v>
+        <v>195.5814407933518</v>
       </c>
       <c r="D26">
-        <v>251.6270462313397</v>
+        <v>252.8164407933518</v>
       </c>
       <c r="E26">
-        <v>29.78</v>
+        <v>32.125</v>
       </c>
       <c r="F26">
-        <v>56.28</v>
+        <v>58.625</v>
       </c>
       <c r="G26">
         <v>1.39</v>
@@ -3419,28 +3419,28 @@
         <v>20.4</v>
       </c>
       <c r="M26">
-        <v>3.056004</v>
+        <v>3.1833375</v>
       </c>
       <c r="N26">
-        <v>17.343996</v>
+        <v>17.2166625</v>
       </c>
       <c r="O26">
-        <v>6.070398599999999</v>
+        <v>6.025831874999999</v>
       </c>
       <c r="P26">
-        <v>11.2735974</v>
+        <v>11.190830625</v>
       </c>
       <c r="Q26">
-        <v>14.1735974</v>
+        <v>14.090830625</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08143228655471464</v>
+        <v>0.08176941881469375</v>
       </c>
       <c r="T26">
-        <v>0.652617841791764</v>
+        <v>0.6587925375292407</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.675383932743542</v>
+        <v>6.408368575433801</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07015081411102032</v>
+        <v>0.06994229044045749</v>
       </c>
       <c r="C27">
-        <v>195.5814407933518</v>
+        <v>194.4371328532819</v>
       </c>
       <c r="D27">
-        <v>252.8164407933518</v>
+        <v>254.0171328532819</v>
       </c>
       <c r="E27">
-        <v>32.125</v>
+        <v>34.47</v>
       </c>
       <c r="F27">
-        <v>58.625</v>
+        <v>60.97</v>
       </c>
       <c r="G27">
         <v>1.39</v>
@@ -3501,28 +3501,28 @@
         <v>20.4</v>
       </c>
       <c r="M27">
-        <v>3.1833375</v>
+        <v>3.310671</v>
       </c>
       <c r="N27">
-        <v>17.2166625</v>
+        <v>17.089329</v>
       </c>
       <c r="O27">
-        <v>6.025831874999999</v>
+        <v>5.98126515</v>
       </c>
       <c r="P27">
-        <v>11.190830625</v>
+        <v>11.10806385</v>
       </c>
       <c r="Q27">
-        <v>14.090830625</v>
+        <v>14.00806385</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08176941881469375</v>
+        <v>0.08211566275737499</v>
       </c>
       <c r="T27">
-        <v>0.6587925375292407</v>
+        <v>0.6651341169352977</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.408368575433801</v>
+        <v>6.16189286099404</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06994229044045749</v>
+        <v>0.06990926676989469</v>
       </c>
       <c r="C28">
-        <v>194.4371328532819</v>
+        <v>192.2833320613012</v>
       </c>
       <c r="D28">
-        <v>254.0171328532819</v>
+        <v>254.2083320613012</v>
       </c>
       <c r="E28">
-        <v>34.47</v>
+        <v>36.815</v>
       </c>
       <c r="F28">
-        <v>60.97</v>
+        <v>63.315</v>
       </c>
       <c r="G28">
         <v>1.39</v>
@@ -3583,45 +3583,45 @@
         <v>20.4</v>
       </c>
       <c r="M28">
-        <v>3.310671</v>
+        <v>3.501319500000001</v>
       </c>
       <c r="N28">
-        <v>17.089329</v>
+        <v>16.8986805</v>
       </c>
       <c r="O28">
-        <v>5.98126515</v>
+        <v>5.914538174999999</v>
       </c>
       <c r="P28">
-        <v>11.10806385</v>
+        <v>10.984142325</v>
       </c>
       <c r="Q28">
-        <v>14.00806385</v>
+        <v>13.884142325</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08211566275737499</v>
+        <v>0.08247139283547217</v>
       </c>
       <c r="T28">
-        <v>0.6651341169352977</v>
+        <v>0.6716494382428907</v>
       </c>
       <c r="U28">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V28">
         <v>0.35</v>
       </c>
       <c r="W28">
-        <v>0.035295</v>
+        <v>0.035945</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>6.16189286099404</v>
+        <v>5.826374885239692</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06990926676989469</v>
+        <v>0.06970724309933186</v>
       </c>
       <c r="C29">
-        <v>192.2833320613012</v>
+        <v>191.1142964834052</v>
       </c>
       <c r="D29">
-        <v>254.2083320613012</v>
+        <v>255.3842964834052</v>
       </c>
       <c r="E29">
-        <v>36.815</v>
+        <v>39.16000000000001</v>
       </c>
       <c r="F29">
-        <v>63.315</v>
+        <v>65.66000000000001</v>
       </c>
       <c r="G29">
         <v>1.39</v>
@@ -3665,28 +3665,28 @@
         <v>20.4</v>
       </c>
       <c r="M29">
-        <v>3.501319500000001</v>
+        <v>3.630998000000001</v>
       </c>
       <c r="N29">
-        <v>16.8986805</v>
+        <v>16.769002</v>
       </c>
       <c r="O29">
-        <v>5.914538174999999</v>
+        <v>5.869150699999999</v>
       </c>
       <c r="P29">
-        <v>10.984142325</v>
+        <v>10.8998513</v>
       </c>
       <c r="Q29">
-        <v>13.884142325</v>
+        <v>13.7998513</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08247139283547217</v>
+        <v>0.08283700430462758</v>
       </c>
       <c r="T29">
-        <v>0.6716494382428907</v>
+        <v>0.6783457406979166</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.826374885239692</v>
+        <v>5.618290067909702</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06970724309933186</v>
+        <v>0.06950521942876904</v>
       </c>
       <c r="C30">
-        <v>191.1142964834052</v>
+        <v>189.9561914622199</v>
       </c>
       <c r="D30">
-        <v>255.3842964834052</v>
+        <v>256.5711914622199</v>
       </c>
       <c r="E30">
-        <v>39.16000000000001</v>
+        <v>41.50500000000001</v>
       </c>
       <c r="F30">
-        <v>65.66000000000001</v>
+        <v>68.00500000000001</v>
       </c>
       <c r="G30">
         <v>1.39</v>
@@ -3747,28 +3747,28 @@
         <v>20.4</v>
       </c>
       <c r="M30">
-        <v>3.630998000000001</v>
+        <v>3.760676500000001</v>
       </c>
       <c r="N30">
-        <v>16.769002</v>
+        <v>16.6393235</v>
       </c>
       <c r="O30">
-        <v>5.869150699999999</v>
+        <v>5.823763224999999</v>
       </c>
       <c r="P30">
-        <v>10.8998513</v>
+        <v>10.815560275</v>
       </c>
       <c r="Q30">
-        <v>13.7998513</v>
+        <v>13.715560275</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08283700430462758</v>
+        <v>0.08321291468840709</v>
       </c>
       <c r="T30">
-        <v>0.6783457406979166</v>
+        <v>0.6852306713911125</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.618290067909702</v>
+        <v>5.424555927636954</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06950521942876904</v>
+        <v>0.06930319575820623</v>
       </c>
       <c r="C31">
-        <v>189.9561914622199</v>
+        <v>188.8091701081561</v>
       </c>
       <c r="D31">
-        <v>256.5711914622199</v>
+        <v>257.7691701081561</v>
       </c>
       <c r="E31">
-        <v>41.505</v>
+        <v>43.84999999999999</v>
       </c>
       <c r="F31">
-        <v>68.005</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="G31">
         <v>1.39</v>
@@ -3829,28 +3829,28 @@
         <v>20.4</v>
       </c>
       <c r="M31">
-        <v>3.7606765</v>
+        <v>3.890355</v>
       </c>
       <c r="N31">
-        <v>16.6393235</v>
+        <v>16.509645</v>
       </c>
       <c r="O31">
-        <v>5.823763225</v>
+        <v>5.778375749999999</v>
       </c>
       <c r="P31">
-        <v>10.815560275</v>
+        <v>10.73126925</v>
       </c>
       <c r="Q31">
-        <v>13.715560275</v>
+        <v>13.63126925</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08321291468840709</v>
+        <v>0.08359956536886604</v>
       </c>
       <c r="T31">
-        <v>0.6852306713911125</v>
+        <v>0.6923123143898281</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.424555927636956</v>
+        <v>5.243737396715724</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06930319575820623</v>
+        <v>0.06910117208764341</v>
       </c>
       <c r="C32">
-        <v>188.8091701081561</v>
+        <v>187.6733884046438</v>
       </c>
       <c r="D32">
-        <v>257.7691701081561</v>
+        <v>258.9783884046438</v>
       </c>
       <c r="E32">
-        <v>43.84999999999999</v>
+        <v>46.19499999999999</v>
       </c>
       <c r="F32">
-        <v>70.34999999999999</v>
+        <v>72.69499999999999</v>
       </c>
       <c r="G32">
         <v>1.39</v>
@@ -3911,28 +3911,28 @@
         <v>20.4</v>
       </c>
       <c r="M32">
-        <v>3.890355</v>
+        <v>4.020033499999999</v>
       </c>
       <c r="N32">
-        <v>16.509645</v>
+        <v>16.3799665</v>
       </c>
       <c r="O32">
-        <v>5.778375749999999</v>
+        <v>5.732988274999999</v>
       </c>
       <c r="P32">
-        <v>10.73126925</v>
+        <v>10.646978225</v>
       </c>
       <c r="Q32">
-        <v>13.63126925</v>
+        <v>13.546978225</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08359956536886604</v>
+        <v>0.08399742331542523</v>
       </c>
       <c r="T32">
-        <v>0.6923123143898281</v>
+        <v>0.6995992224029994</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.243737396715724</v>
+        <v>5.07458457746683</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06910117208764341</v>
+        <v>0.06889914841708059</v>
       </c>
       <c r="C33">
-        <v>187.6733884046438</v>
+        <v>186.5490052758367</v>
       </c>
       <c r="D33">
-        <v>258.9783884046438</v>
+        <v>260.1990052758367</v>
       </c>
       <c r="E33">
-        <v>46.19499999999999</v>
+        <v>48.54000000000001</v>
       </c>
       <c r="F33">
-        <v>72.69499999999999</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="G33">
         <v>1.39</v>
@@ -3993,28 +3993,28 @@
         <v>20.4</v>
       </c>
       <c r="M33">
-        <v>4.020033499999999</v>
+        <v>4.149712</v>
       </c>
       <c r="N33">
-        <v>16.3799665</v>
+        <v>16.250288</v>
       </c>
       <c r="O33">
-        <v>5.732988274999999</v>
+        <v>5.687600799999998</v>
       </c>
       <c r="P33">
-        <v>10.646978225</v>
+        <v>10.5626872</v>
       </c>
       <c r="Q33">
-        <v>13.546978225</v>
+        <v>13.4626872</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08399742331542523</v>
+        <v>0.08440698296629498</v>
       </c>
       <c r="T33">
-        <v>0.6995992224029994</v>
+        <v>0.7071004512400875</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.07458457746683</v>
+        <v>4.916003809420991</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06889914841708059</v>
+        <v>0.06869712474651776</v>
       </c>
       <c r="C34">
-        <v>186.5490052758367</v>
+        <v>185.4361826562426</v>
       </c>
       <c r="D34">
-        <v>260.1990052758367</v>
+        <v>261.4311826562426</v>
       </c>
       <c r="E34">
-        <v>48.54000000000001</v>
+        <v>50.88500000000001</v>
       </c>
       <c r="F34">
-        <v>75.04000000000001</v>
+        <v>77.38500000000001</v>
       </c>
       <c r="G34">
         <v>1.39</v>
@@ -4075,28 +4075,28 @@
         <v>20.4</v>
       </c>
       <c r="M34">
-        <v>4.149712</v>
+        <v>4.279390500000001</v>
       </c>
       <c r="N34">
-        <v>16.250288</v>
+        <v>16.1206095</v>
       </c>
       <c r="O34">
-        <v>5.687600799999998</v>
+        <v>5.642213324999998</v>
       </c>
       <c r="P34">
-        <v>10.5626872</v>
+        <v>10.478396175</v>
       </c>
       <c r="Q34">
-        <v>13.4626872</v>
+        <v>13.378396175</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08440698296629498</v>
+        <v>0.08482876827838473</v>
       </c>
       <c r="T34">
-        <v>0.7071004512400875</v>
+        <v>0.7148255973558945</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.916003809420991</v>
+        <v>4.767033997014293</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06869712474651776</v>
+        <v>0.06849510107595495</v>
       </c>
       <c r="C35">
-        <v>185.4361826562426</v>
+        <v>184.3350855623391</v>
       </c>
       <c r="D35">
-        <v>261.4311826562426</v>
+        <v>262.6750855623391</v>
       </c>
       <c r="E35">
-        <v>50.88500000000001</v>
+        <v>53.23</v>
       </c>
       <c r="F35">
-        <v>77.38500000000001</v>
+        <v>79.73</v>
       </c>
       <c r="G35">
         <v>1.39</v>
@@ -4157,28 +4157,28 @@
         <v>20.4</v>
       </c>
       <c r="M35">
-        <v>4.279390500000001</v>
+        <v>4.409069000000001</v>
       </c>
       <c r="N35">
-        <v>16.1206095</v>
+        <v>15.990931</v>
       </c>
       <c r="O35">
-        <v>5.642213324999998</v>
+        <v>5.596825849999999</v>
       </c>
       <c r="P35">
-        <v>10.478396175</v>
+        <v>10.39410515</v>
       </c>
       <c r="Q35">
-        <v>13.378396175</v>
+        <v>13.29410515</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08482876827838473</v>
+        <v>0.08526333496356811</v>
       </c>
       <c r="T35">
-        <v>0.7148255973558945</v>
+        <v>0.7227848388085443</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.767033997014293</v>
+        <v>4.626827114749167</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06849510107595495</v>
+        <v>0.06886182740539214</v>
       </c>
       <c r="C36">
-        <v>184.3350855623391</v>
+        <v>179.740757173555</v>
       </c>
       <c r="D36">
-        <v>262.6750855623391</v>
+        <v>260.425757173555</v>
       </c>
       <c r="E36">
-        <v>53.23</v>
+        <v>55.575</v>
       </c>
       <c r="F36">
-        <v>79.73</v>
+        <v>82.075</v>
       </c>
       <c r="G36">
         <v>1.39</v>
@@ -4239,45 +4239,45 @@
         <v>20.4</v>
       </c>
       <c r="M36">
-        <v>4.409069000000001</v>
+        <v>4.743935</v>
       </c>
       <c r="N36">
-        <v>15.990931</v>
+        <v>15.656065</v>
       </c>
       <c r="O36">
-        <v>5.596825849999999</v>
+        <v>5.479622749999999</v>
       </c>
       <c r="P36">
-        <v>10.39410515</v>
+        <v>10.17644225</v>
       </c>
       <c r="Q36">
-        <v>13.29410515</v>
+        <v>13.07644225</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08526333496356811</v>
+        <v>0.08571127293137251</v>
       </c>
       <c r="T36">
-        <v>0.7227848388085443</v>
+        <v>0.7309889799981986</v>
       </c>
       <c r="U36">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V36">
         <v>0.35</v>
       </c>
       <c r="W36">
-        <v>0.035945</v>
+        <v>0.03757000000000001</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>4.626827114749167</v>
+        <v>4.30022755370805</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06886182740539214</v>
+        <v>0.06867605373482931</v>
       </c>
       <c r="C37">
-        <v>179.740757173555</v>
+        <v>178.5303708049994</v>
       </c>
       <c r="D37">
-        <v>260.425757173555</v>
+        <v>261.5603708049994</v>
       </c>
       <c r="E37">
-        <v>55.575</v>
+        <v>57.92000000000002</v>
       </c>
       <c r="F37">
-        <v>82.075</v>
+        <v>84.42000000000002</v>
       </c>
       <c r="G37">
         <v>1.39</v>
@@ -4321,28 +4321,28 @@
         <v>20.4</v>
       </c>
       <c r="M37">
-        <v>4.743935</v>
+        <v>4.879476000000001</v>
       </c>
       <c r="N37">
-        <v>15.656065</v>
+        <v>15.520524</v>
       </c>
       <c r="O37">
-        <v>5.479622749999999</v>
+        <v>5.432183399999999</v>
       </c>
       <c r="P37">
-        <v>10.17644225</v>
+        <v>10.0883406</v>
       </c>
       <c r="Q37">
-        <v>13.07644225</v>
+        <v>12.9883406</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08571127293137251</v>
+        <v>0.08617320896067081</v>
       </c>
       <c r="T37">
-        <v>0.7309889799981986</v>
+        <v>0.7394495006000296</v>
       </c>
       <c r="U37">
         <v>0.0578</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.30022755370805</v>
+        <v>4.18077678832727</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06867605373482932</v>
+        <v>0.0684902800642665</v>
       </c>
       <c r="C38">
-        <v>178.5303708049993</v>
+        <v>177.3299141862615</v>
       </c>
       <c r="D38">
-        <v>261.5603708049994</v>
+        <v>262.7049141862615</v>
       </c>
       <c r="E38">
-        <v>57.92</v>
+        <v>60.265</v>
       </c>
       <c r="F38">
-        <v>84.42</v>
+        <v>86.765</v>
       </c>
       <c r="G38">
         <v>1.39</v>
@@ -4403,28 +4403,28 @@
         <v>20.4</v>
       </c>
       <c r="M38">
-        <v>4.879476</v>
+        <v>5.015017</v>
       </c>
       <c r="N38">
-        <v>15.520524</v>
+        <v>15.384983</v>
       </c>
       <c r="O38">
-        <v>5.432183399999999</v>
+        <v>5.384744049999999</v>
       </c>
       <c r="P38">
-        <v>10.0883406</v>
+        <v>10.00023895</v>
       </c>
       <c r="Q38">
-        <v>12.9883406</v>
+        <v>12.90023895</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08617320896067081</v>
+        <v>0.08664980962581983</v>
       </c>
       <c r="T38">
-        <v>0.7394495006000296</v>
+        <v>0.7481786091574741</v>
       </c>
       <c r="U38">
         <v>0.0578</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.18077678832727</v>
+        <v>4.067782821075182</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0684902800642665</v>
+        <v>0.06916900639370369</v>
       </c>
       <c r="C39">
-        <v>177.3299141862615</v>
+        <v>170.8511011213253</v>
       </c>
       <c r="D39">
-        <v>262.7049141862615</v>
+        <v>258.5711011213253</v>
       </c>
       <c r="E39">
-        <v>60.265</v>
+        <v>62.61</v>
       </c>
       <c r="F39">
-        <v>86.765</v>
+        <v>89.11</v>
       </c>
       <c r="G39">
         <v>1.39</v>
@@ -4485,45 +4485,45 @@
         <v>20.4</v>
       </c>
       <c r="M39">
-        <v>5.015017</v>
+        <v>5.462443</v>
       </c>
       <c r="N39">
-        <v>15.384983</v>
+        <v>14.937557</v>
       </c>
       <c r="O39">
-        <v>5.384744049999999</v>
+        <v>5.228144949999999</v>
       </c>
       <c r="P39">
-        <v>10.00023895</v>
+        <v>9.709412049999999</v>
       </c>
       <c r="Q39">
-        <v>12.90023895</v>
+        <v>12.60941205</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08664980962581983</v>
+        <v>0.08714178450597368</v>
       </c>
       <c r="T39">
-        <v>0.7481786091574741</v>
+        <v>0.7571893018619332</v>
       </c>
       <c r="U39">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V39">
         <v>0.35</v>
       </c>
       <c r="W39">
-        <v>0.03757000000000001</v>
+        <v>0.039845</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y39">
-        <v>4.067782821075182</v>
+        <v>3.734592745407137</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06916900639370369</v>
+        <v>0.06900598272314086</v>
       </c>
       <c r="C40">
-        <v>170.8511011213253</v>
+        <v>169.4870878540548</v>
       </c>
       <c r="D40">
-        <v>258.5711011213253</v>
+        <v>259.5520878540548</v>
       </c>
       <c r="E40">
-        <v>62.61</v>
+        <v>64.955</v>
       </c>
       <c r="F40">
-        <v>89.11</v>
+        <v>91.455</v>
       </c>
       <c r="G40">
         <v>1.39</v>
@@ -4567,28 +4567,28 @@
         <v>20.4</v>
       </c>
       <c r="M40">
-        <v>5.462443</v>
+        <v>5.6061915</v>
       </c>
       <c r="N40">
-        <v>14.937557</v>
+        <v>14.7938085</v>
       </c>
       <c r="O40">
-        <v>5.228144949999999</v>
+        <v>5.177832974999999</v>
       </c>
       <c r="P40">
-        <v>9.709412049999999</v>
+        <v>9.615975525</v>
       </c>
       <c r="Q40">
-        <v>12.60941205</v>
+        <v>12.515975525</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08714178450597368</v>
+        <v>0.08764988971006699</v>
       </c>
       <c r="T40">
-        <v>0.7571893018619332</v>
+        <v>0.7664954271140795</v>
       </c>
       <c r="U40">
         <v>0.0613</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.734592745407137</v>
+        <v>3.638833957063365</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06900598272314086</v>
+        <v>0.06884295905257805</v>
       </c>
       <c r="C41">
-        <v>169.4870878540548</v>
+        <v>168.1305464183185</v>
       </c>
       <c r="D41">
-        <v>259.5520878540548</v>
+        <v>260.5405464183186</v>
       </c>
       <c r="E41">
-        <v>64.955</v>
+        <v>67.30000000000001</v>
       </c>
       <c r="F41">
-        <v>91.455</v>
+        <v>93.80000000000001</v>
       </c>
       <c r="G41">
         <v>1.39</v>
@@ -4649,28 +4649,28 @@
         <v>20.4</v>
       </c>
       <c r="M41">
-        <v>5.6061915</v>
+        <v>5.74994</v>
       </c>
       <c r="N41">
-        <v>14.7938085</v>
+        <v>14.65006</v>
       </c>
       <c r="O41">
-        <v>5.177832974999999</v>
+        <v>5.127520999999999</v>
       </c>
       <c r="P41">
-        <v>9.615975525</v>
+        <v>9.522538999999998</v>
       </c>
       <c r="Q41">
-        <v>12.515975525</v>
+        <v>12.422539</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08764988971006699</v>
+        <v>0.08817493175429675</v>
       </c>
       <c r="T41">
-        <v>0.7664954271140795</v>
+        <v>0.7761117565412972</v>
       </c>
       <c r="U41">
         <v>0.0613</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.638833957063365</v>
+        <v>3.54786310813678</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.06884295905257805</v>
+        <v>0.06942613538201524</v>
       </c>
       <c r="C42">
-        <v>168.1305464183185</v>
+        <v>162.2838226343621</v>
       </c>
       <c r="D42">
-        <v>260.5405464183186</v>
+        <v>257.0388226343621</v>
       </c>
       <c r="E42">
-        <v>67.30000000000001</v>
+        <v>69.64500000000001</v>
       </c>
       <c r="F42">
-        <v>93.80000000000001</v>
+        <v>96.14500000000001</v>
       </c>
       <c r="G42">
         <v>1.39</v>
@@ -4731,45 +4731,45 @@
         <v>20.4</v>
       </c>
       <c r="M42">
-        <v>5.74994</v>
+        <v>6.162894500000001</v>
       </c>
       <c r="N42">
-        <v>14.65006</v>
+        <v>14.2371055</v>
       </c>
       <c r="O42">
-        <v>5.127520999999999</v>
+        <v>4.982986924999999</v>
       </c>
       <c r="P42">
-        <v>9.522538999999998</v>
+        <v>9.254118575</v>
       </c>
       <c r="Q42">
-        <v>12.422539</v>
+        <v>12.154118575</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08817493175429675</v>
+        <v>0.08871777183392413</v>
       </c>
       <c r="T42">
-        <v>0.7761117565412972</v>
+        <v>0.7860540632372341</v>
       </c>
       <c r="U42">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V42">
         <v>0.35</v>
       </c>
       <c r="W42">
-        <v>0.039845</v>
+        <v>0.04166500000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>3.54786310813678</v>
+        <v>3.310132925364858</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.06942613538201524</v>
+        <v>0.06928131171145241</v>
       </c>
       <c r="C43">
-        <v>162.2838226343621</v>
+        <v>160.7996120487116</v>
       </c>
       <c r="D43">
-        <v>257.0388226343621</v>
+        <v>257.8996120487116</v>
       </c>
       <c r="E43">
-        <v>69.64500000000001</v>
+        <v>71.99000000000001</v>
       </c>
       <c r="F43">
-        <v>96.14500000000001</v>
+        <v>98.49000000000001</v>
       </c>
       <c r="G43">
         <v>1.39</v>
@@ -4813,28 +4813,28 @@
         <v>20.4</v>
       </c>
       <c r="M43">
-        <v>6.162894500000001</v>
+        <v>6.313209000000001</v>
       </c>
       <c r="N43">
-        <v>14.2371055</v>
+        <v>14.086791</v>
       </c>
       <c r="O43">
-        <v>4.982986924999999</v>
+        <v>4.930376849999999</v>
       </c>
       <c r="P43">
-        <v>9.254118575</v>
+        <v>9.15641415</v>
       </c>
       <c r="Q43">
-        <v>12.154118575</v>
+        <v>12.05641415</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08871777183392413</v>
+        <v>0.08927933053698692</v>
       </c>
       <c r="T43">
-        <v>0.7860540632372341</v>
+        <v>0.7963392080950999</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.310132925364858</v>
+        <v>3.231320236665695</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06928131171145242</v>
+        <v>0.06913648804088961</v>
       </c>
       <c r="C44">
-        <v>160.7996120487115</v>
+        <v>159.3211861777497</v>
       </c>
       <c r="D44">
-        <v>257.8996120487115</v>
+        <v>258.7661861777497</v>
       </c>
       <c r="E44">
-        <v>71.98999999999999</v>
+        <v>74.33499999999999</v>
       </c>
       <c r="F44">
-        <v>98.48999999999999</v>
+        <v>100.835</v>
       </c>
       <c r="G44">
         <v>1.39</v>
@@ -4895,28 +4895,28 @@
         <v>20.4</v>
       </c>
       <c r="M44">
-        <v>6.313209000000001</v>
+        <v>6.4635235</v>
       </c>
       <c r="N44">
-        <v>14.086791</v>
+        <v>13.9364765</v>
       </c>
       <c r="O44">
-        <v>4.930376849999999</v>
+        <v>4.877766774999999</v>
       </c>
       <c r="P44">
-        <v>9.15641415</v>
+        <v>9.058709725</v>
       </c>
       <c r="Q44">
-        <v>12.05641415</v>
+        <v>11.958709725</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08927933053698692</v>
+        <v>0.08986059305419228</v>
       </c>
       <c r="T44">
-        <v>0.7963392080950999</v>
+        <v>0.8069852352286805</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.231320236665695</v>
+        <v>3.156173254417656</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.06913648804088961</v>
+        <v>0.06899166437032678</v>
       </c>
       <c r="C45">
-        <v>159.3211861777497</v>
+        <v>157.848603530112</v>
       </c>
       <c r="D45">
-        <v>258.7661861777497</v>
+        <v>259.6386035301121</v>
       </c>
       <c r="E45">
-        <v>74.33499999999999</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="F45">
-        <v>100.835</v>
+        <v>103.18</v>
       </c>
       <c r="G45">
         <v>1.39</v>
@@ -4977,28 +4977,28 @@
         <v>20.4</v>
       </c>
       <c r="M45">
-        <v>6.4635235</v>
+        <v>6.613838000000001</v>
       </c>
       <c r="N45">
-        <v>13.9364765</v>
+        <v>13.786162</v>
       </c>
       <c r="O45">
-        <v>4.877766774999999</v>
+        <v>4.825156699999999</v>
       </c>
       <c r="P45">
-        <v>9.058709725</v>
+        <v>8.961005299999998</v>
       </c>
       <c r="Q45">
-        <v>11.958709725</v>
+        <v>11.8610053</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08986059305419228</v>
+        <v>0.0904626149470121</v>
       </c>
       <c r="T45">
-        <v>0.8069852352286805</v>
+        <v>0.8180114776170316</v>
       </c>
       <c r="U45">
         <v>0.0641</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.156173254417656</v>
+        <v>3.084442044089982</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.06899166437032678</v>
+        <v>0.06884684069976396</v>
       </c>
       <c r="C46">
-        <v>157.848603530112</v>
+        <v>156.3819234061387</v>
       </c>
       <c r="D46">
-        <v>259.6386035301121</v>
+        <v>260.5169234061387</v>
       </c>
       <c r="E46">
-        <v>76.68000000000001</v>
+        <v>79.02500000000001</v>
       </c>
       <c r="F46">
-        <v>103.18</v>
+        <v>105.525</v>
       </c>
       <c r="G46">
         <v>1.39</v>
@@ -5059,28 +5059,28 @@
         <v>20.4</v>
       </c>
       <c r="M46">
-        <v>6.613838000000001</v>
+        <v>6.764152500000001</v>
       </c>
       <c r="N46">
-        <v>13.786162</v>
+        <v>13.6358475</v>
       </c>
       <c r="O46">
-        <v>4.825156699999999</v>
+        <v>4.772546624999999</v>
       </c>
       <c r="P46">
-        <v>8.961005299999998</v>
+        <v>8.863300874999998</v>
       </c>
       <c r="Q46">
-        <v>11.8610053</v>
+        <v>11.763300875</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.0904626149470121</v>
+        <v>0.09108652854502537</v>
       </c>
       <c r="T46">
-        <v>0.8180114776170316</v>
+        <v>0.82943867427405</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.084442044089982</v>
+        <v>3.015898887554649</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.06884684069976396</v>
+        <v>0.07103421702920115</v>
       </c>
       <c r="C47">
-        <v>156.3819234061387</v>
+        <v>141.3731856343471</v>
       </c>
       <c r="D47">
-        <v>260.5169234061387</v>
+        <v>247.8531856343471</v>
       </c>
       <c r="E47">
-        <v>79.02500000000001</v>
+        <v>81.37</v>
       </c>
       <c r="F47">
-        <v>105.525</v>
+        <v>107.87</v>
       </c>
       <c r="G47">
         <v>1.39</v>
@@ -5141,45 +5141,45 @@
         <v>20.4</v>
       </c>
       <c r="M47">
-        <v>6.764152500000001</v>
+        <v>7.755853000000001</v>
       </c>
       <c r="N47">
-        <v>13.6358475</v>
+        <v>12.644147</v>
       </c>
       <c r="O47">
-        <v>4.772546624999999</v>
+        <v>4.425451449999999</v>
       </c>
       <c r="P47">
-        <v>8.863300874999998</v>
+        <v>8.218695549999998</v>
       </c>
       <c r="Q47">
-        <v>11.763300875</v>
+        <v>11.11869555</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09108652854502537</v>
+        <v>0.09173355005407619</v>
       </c>
       <c r="T47">
-        <v>0.82943867427405</v>
+        <v>0.8412891004368842</v>
       </c>
       <c r="U47">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V47">
         <v>0.35</v>
       </c>
       <c r="W47">
-        <v>0.04166500000000001</v>
+        <v>0.04673500000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>3.015898887554649</v>
+        <v>2.630271615514115</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07103421702920115</v>
+        <v>0.07094009335863832</v>
       </c>
       <c r="C48">
-        <v>141.3731856343471</v>
+        <v>139.5477091255048</v>
       </c>
       <c r="D48">
-        <v>247.8531856343471</v>
+        <v>248.3727091255049</v>
       </c>
       <c r="E48">
-        <v>81.37</v>
+        <v>83.715</v>
       </c>
       <c r="F48">
-        <v>107.87</v>
+        <v>110.215</v>
       </c>
       <c r="G48">
         <v>1.39</v>
@@ -5223,28 +5223,28 @@
         <v>20.4</v>
       </c>
       <c r="M48">
-        <v>7.755853000000001</v>
+        <v>7.924458500000001</v>
       </c>
       <c r="N48">
-        <v>12.644147</v>
+        <v>12.4755415</v>
       </c>
       <c r="O48">
-        <v>4.425451449999999</v>
+        <v>4.366439524999999</v>
       </c>
       <c r="P48">
-        <v>8.218695549999998</v>
+        <v>8.109101975</v>
       </c>
       <c r="Q48">
-        <v>11.11869555</v>
+        <v>11.009101975</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09173355005407619</v>
+        <v>0.09240498746912891</v>
       </c>
       <c r="T48">
-        <v>0.8412891004368842</v>
+        <v>0.8535867124926553</v>
       </c>
       <c r="U48">
         <v>0.07190000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.630271615514115</v>
+        <v>2.574308389652113</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07094009335863832</v>
+        <v>0.07084596968807552</v>
       </c>
       <c r="C49">
-        <v>139.5477091255048</v>
+        <v>137.72441513121</v>
       </c>
       <c r="D49">
-        <v>248.3727091255049</v>
+        <v>248.89441513121</v>
       </c>
       <c r="E49">
-        <v>83.715</v>
+        <v>86.06</v>
       </c>
       <c r="F49">
-        <v>110.215</v>
+        <v>112.56</v>
       </c>
       <c r="G49">
         <v>1.39</v>
@@ -5305,28 +5305,28 @@
         <v>20.4</v>
       </c>
       <c r="M49">
-        <v>7.924458500000001</v>
+        <v>8.093064</v>
       </c>
       <c r="N49">
-        <v>12.4755415</v>
+        <v>12.306936</v>
       </c>
       <c r="O49">
-        <v>4.366439524999999</v>
+        <v>4.3074276</v>
       </c>
       <c r="P49">
-        <v>8.109101975</v>
+        <v>7.999508399999999</v>
       </c>
       <c r="Q49">
-        <v>11.009101975</v>
+        <v>10.8995084</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09240498746912891</v>
+        <v>0.09310224940014521</v>
       </c>
       <c r="T49">
-        <v>0.8535867124926553</v>
+        <v>0.8663573096274946</v>
       </c>
       <c r="U49">
         <v>0.07190000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.574308389652113</v>
+        <v>2.520676964867694</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07084596968807552</v>
+        <v>0.07199399601751269</v>
       </c>
       <c r="C50">
-        <v>137.72441513121</v>
+        <v>129.1620878414813</v>
       </c>
       <c r="D50">
-        <v>248.89441513121</v>
+        <v>242.6770878414813</v>
       </c>
       <c r="E50">
-        <v>86.06</v>
+        <v>88.405</v>
       </c>
       <c r="F50">
-        <v>112.56</v>
+        <v>114.905</v>
       </c>
       <c r="G50">
         <v>1.39</v>
@@ -5387,45 +5387,45 @@
         <v>20.4</v>
       </c>
       <c r="M50">
-        <v>8.093064</v>
+        <v>8.709799</v>
       </c>
       <c r="N50">
-        <v>12.306936</v>
+        <v>11.690201</v>
       </c>
       <c r="O50">
-        <v>4.3074276</v>
+        <v>4.09157035</v>
       </c>
       <c r="P50">
-        <v>7.999508399999999</v>
+        <v>7.598630649999999</v>
       </c>
       <c r="Q50">
-        <v>10.8995084</v>
+        <v>10.49863065</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09310224940014521</v>
+        <v>0.09382685493629939</v>
       </c>
       <c r="T50">
-        <v>0.8663573096274946</v>
+        <v>0.8796287144931118</v>
       </c>
       <c r="U50">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V50">
         <v>0.35</v>
       </c>
       <c r="W50">
-        <v>0.04673500000000001</v>
+        <v>0.04927000000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.520676964867694</v>
+        <v>2.342189526991381</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07199399601751269</v>
+        <v>0.07192522234694987</v>
       </c>
       <c r="C51">
-        <v>129.1620878414813</v>
+        <v>127.1807834776563</v>
       </c>
       <c r="D51">
-        <v>242.6770878414813</v>
+        <v>243.0407834776563</v>
       </c>
       <c r="E51">
-        <v>88.405</v>
+        <v>90.75</v>
       </c>
       <c r="F51">
-        <v>114.905</v>
+        <v>117.25</v>
       </c>
       <c r="G51">
         <v>1.39</v>
@@ -5469,28 +5469,28 @@
         <v>20.4</v>
       </c>
       <c r="M51">
-        <v>8.709799</v>
+        <v>8.887550000000001</v>
       </c>
       <c r="N51">
-        <v>11.690201</v>
+        <v>11.51245</v>
       </c>
       <c r="O51">
-        <v>4.09157035</v>
+        <v>4.029357499999999</v>
       </c>
       <c r="P51">
-        <v>7.598630649999999</v>
+        <v>7.483092499999999</v>
       </c>
       <c r="Q51">
-        <v>10.49863065</v>
+        <v>10.3830925</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09382685493629939</v>
+        <v>0.09458044469389973</v>
       </c>
       <c r="T51">
-        <v>0.8796287144931118</v>
+        <v>0.8934309755533536</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.342189526991381</v>
+        <v>2.295345736451552</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07192522234694987</v>
+        <v>0.07185644867638706</v>
       </c>
       <c r="C52">
-        <v>127.1807834776563</v>
+        <v>125.2005708778032</v>
       </c>
       <c r="D52">
-        <v>243.0407834776563</v>
+        <v>243.4055708778032</v>
       </c>
       <c r="E52">
-        <v>90.75</v>
+        <v>93.095</v>
       </c>
       <c r="F52">
-        <v>117.25</v>
+        <v>119.595</v>
       </c>
       <c r="G52">
         <v>1.39</v>
@@ -5551,28 +5551,28 @@
         <v>20.4</v>
       </c>
       <c r="M52">
-        <v>8.887550000000001</v>
+        <v>9.065301</v>
       </c>
       <c r="N52">
-        <v>11.51245</v>
+        <v>11.334699</v>
       </c>
       <c r="O52">
-        <v>4.029357499999999</v>
+        <v>3.967144649999999</v>
       </c>
       <c r="P52">
-        <v>7.483092499999999</v>
+        <v>7.367554349999999</v>
       </c>
       <c r="Q52">
-        <v>10.3830925</v>
+        <v>10.26755435</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09458044469389973</v>
+        <v>0.09536479321711644</v>
       </c>
       <c r="T52">
-        <v>0.8934309755533536</v>
+        <v>0.9077965942078913</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.295345736451552</v>
+        <v>2.250338957305444</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07185644867638706</v>
+        <v>0.07178767500582424</v>
       </c>
       <c r="C53">
-        <v>125.2005708778032</v>
+        <v>123.2214549652984</v>
       </c>
       <c r="D53">
-        <v>243.4055708778032</v>
+        <v>243.7714549652984</v>
       </c>
       <c r="E53">
-        <v>93.095</v>
+        <v>95.44</v>
       </c>
       <c r="F53">
-        <v>119.595</v>
+        <v>121.94</v>
       </c>
       <c r="G53">
         <v>1.39</v>
@@ -5633,28 +5633,28 @@
         <v>20.4</v>
       </c>
       <c r="M53">
-        <v>9.065301</v>
+        <v>9.243052</v>
       </c>
       <c r="N53">
-        <v>11.334699</v>
+        <v>11.156948</v>
       </c>
       <c r="O53">
-        <v>3.967144649999999</v>
+        <v>3.904931799999999</v>
       </c>
       <c r="P53">
-        <v>7.367554349999999</v>
+        <v>7.252016199999999</v>
       </c>
       <c r="Q53">
-        <v>10.26755435</v>
+        <v>10.1520162</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09536479321711644</v>
+        <v>0.09618182292880048</v>
       </c>
       <c r="T53">
-        <v>0.9077965942078913</v>
+        <v>0.9227607803063679</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.250338957305444</v>
+        <v>2.207063208126493</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07178767500582424</v>
+        <v>0.07171890133526143</v>
       </c>
       <c r="C54">
-        <v>123.2214549652984</v>
+        <v>121.2434406931655</v>
       </c>
       <c r="D54">
-        <v>243.7714549652984</v>
+        <v>244.1384406931655</v>
       </c>
       <c r="E54">
-        <v>95.44</v>
+        <v>97.78500000000001</v>
       </c>
       <c r="F54">
-        <v>121.94</v>
+        <v>124.285</v>
       </c>
       <c r="G54">
         <v>1.39</v>
@@ -5715,28 +5715,28 @@
         <v>20.4</v>
       </c>
       <c r="M54">
-        <v>9.243052</v>
+        <v>9.420803000000001</v>
       </c>
       <c r="N54">
-        <v>11.156948</v>
+        <v>10.979197</v>
       </c>
       <c r="O54">
-        <v>3.904931799999999</v>
+        <v>3.842718949999999</v>
       </c>
       <c r="P54">
-        <v>7.252016199999999</v>
+        <v>7.136478049999999</v>
       </c>
       <c r="Q54">
-        <v>10.1520162</v>
+        <v>10.03647805</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09618182292880048</v>
+        <v>0.09703361986225834</v>
       </c>
       <c r="T54">
-        <v>0.9227607803063679</v>
+        <v>0.9383617402813754</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.207063208126493</v>
+        <v>2.16542050608637</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07171890133526143</v>
+        <v>0.0716501276646986</v>
       </c>
       <c r="C55">
-        <v>121.2434406931655</v>
+        <v>119.2665330442996</v>
       </c>
       <c r="D55">
-        <v>244.1384406931655</v>
+        <v>244.5065330442996</v>
       </c>
       <c r="E55">
-        <v>97.78500000000001</v>
+        <v>100.13</v>
       </c>
       <c r="F55">
-        <v>124.285</v>
+        <v>126.63</v>
       </c>
       <c r="G55">
         <v>1.39</v>
@@ -5797,28 +5797,28 @@
         <v>20.4</v>
       </c>
       <c r="M55">
-        <v>9.420803000000001</v>
+        <v>9.598554000000002</v>
       </c>
       <c r="N55">
-        <v>10.979197</v>
+        <v>10.801446</v>
       </c>
       <c r="O55">
-        <v>3.842718949999999</v>
+        <v>3.780506099999998</v>
       </c>
       <c r="P55">
-        <v>7.136478049999999</v>
+        <v>7.020939899999998</v>
       </c>
       <c r="Q55">
-        <v>10.03647805</v>
+        <v>9.9209399</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09703361986225834</v>
+        <v>0.09792245144499695</v>
       </c>
       <c r="T55">
-        <v>0.9383617402813754</v>
+        <v>0.954641002863992</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.16542050608637</v>
+        <v>2.12532012634403</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.0716501276646986</v>
+        <v>0.07158135399413579</v>
       </c>
       <c r="C56">
-        <v>119.2665330442996</v>
+        <v>117.2907370316919</v>
       </c>
       <c r="D56">
-        <v>244.5065330442996</v>
+        <v>244.8757370316919</v>
       </c>
       <c r="E56">
-        <v>100.13</v>
+        <v>102.475</v>
       </c>
       <c r="F56">
-        <v>126.63</v>
+        <v>128.975</v>
       </c>
       <c r="G56">
         <v>1.39</v>
@@ -5879,28 +5879,28 @@
         <v>20.4</v>
       </c>
       <c r="M56">
-        <v>9.598554000000002</v>
+        <v>9.776305000000002</v>
       </c>
       <c r="N56">
-        <v>10.801446</v>
+        <v>10.623695</v>
       </c>
       <c r="O56">
-        <v>3.780506099999998</v>
+        <v>3.718293249999999</v>
       </c>
       <c r="P56">
-        <v>7.020939899999998</v>
+        <v>6.905401749999998</v>
       </c>
       <c r="Q56">
-        <v>9.9209399</v>
+        <v>9.80540175</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09792245144499695</v>
+        <v>0.09885078665363507</v>
       </c>
       <c r="T56">
-        <v>0.954641002863992</v>
+        <v>0.9716437882280582</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.12532012634403</v>
+        <v>2.086677942228684</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07158135399413579</v>
+        <v>0.07151258032357297</v>
       </c>
       <c r="C57">
-        <v>117.2907370316919</v>
+        <v>115.3160576986583</v>
       </c>
       <c r="D57">
-        <v>244.8757370316919</v>
+        <v>245.2460576986583</v>
       </c>
       <c r="E57">
-        <v>102.475</v>
+        <v>104.82</v>
       </c>
       <c r="F57">
-        <v>128.975</v>
+        <v>131.32</v>
       </c>
       <c r="G57">
         <v>1.39</v>
@@ -5961,28 +5961,28 @@
         <v>20.4</v>
       </c>
       <c r="M57">
-        <v>9.776305000000002</v>
+        <v>9.954056000000003</v>
       </c>
       <c r="N57">
-        <v>10.623695</v>
+        <v>10.445944</v>
       </c>
       <c r="O57">
-        <v>3.718293249999999</v>
+        <v>3.656080399999998</v>
       </c>
       <c r="P57">
-        <v>6.905401749999998</v>
+        <v>6.789863599999997</v>
       </c>
       <c r="Q57">
-        <v>9.80540175</v>
+        <v>9.689863599999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09885078665363507</v>
+        <v>0.09982131891721129</v>
       </c>
       <c r="T57">
-        <v>0.9716437882280582</v>
+        <v>0.9894194274723092</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.086677942228684</v>
+        <v>2.049415836117457</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07151258032357297</v>
+        <v>0.07144380665301014</v>
       </c>
       <c r="C58">
-        <v>115.3160576986583</v>
+        <v>113.3425001190682</v>
       </c>
       <c r="D58">
-        <v>245.2460576986583</v>
+        <v>245.6175001190682</v>
       </c>
       <c r="E58">
-        <v>104.82</v>
+        <v>107.165</v>
       </c>
       <c r="F58">
-        <v>131.32</v>
+        <v>133.665</v>
       </c>
       <c r="G58">
         <v>1.39</v>
@@ -6043,28 +6043,28 @@
         <v>20.4</v>
       </c>
       <c r="M58">
-        <v>9.954056000000003</v>
+        <v>10.131807</v>
       </c>
       <c r="N58">
-        <v>10.445944</v>
+        <v>10.268193</v>
       </c>
       <c r="O58">
-        <v>3.656080399999998</v>
+        <v>3.593867549999998</v>
       </c>
       <c r="P58">
-        <v>6.789863599999997</v>
+        <v>6.674325449999998</v>
       </c>
       <c r="Q58">
-        <v>9.689863599999999</v>
+        <v>9.57432545</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09982131891721129</v>
+        <v>0.1008369922163027</v>
       </c>
       <c r="T58">
-        <v>0.9894194274723092</v>
+        <v>1.008021840634897</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.049415836117457</v>
+        <v>2.013461172325923</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07144380665301014</v>
+        <v>0.07672843298244733</v>
       </c>
       <c r="C59">
-        <v>113.3425001190682</v>
+        <v>85.39228242858977</v>
       </c>
       <c r="D59">
-        <v>245.6175001190682</v>
+        <v>220.0122824285898</v>
       </c>
       <c r="E59">
-        <v>107.165</v>
+        <v>109.51</v>
       </c>
       <c r="F59">
-        <v>133.665</v>
+        <v>136.01</v>
       </c>
       <c r="G59">
         <v>1.39</v>
@@ -6125,45 +6125,45 @@
         <v>20.4</v>
       </c>
       <c r="M59">
-        <v>10.131807</v>
+        <v>12.2409</v>
       </c>
       <c r="N59">
-        <v>10.268193</v>
+        <v>8.159099999999997</v>
       </c>
       <c r="O59">
-        <v>3.593867549999998</v>
+        <v>2.855684999999999</v>
       </c>
       <c r="P59">
-        <v>6.674325449999998</v>
+        <v>5.303414999999998</v>
       </c>
       <c r="Q59">
-        <v>9.57432545</v>
+        <v>8.203415</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1008369922163027</v>
+        <v>0.1019010309105889</v>
       </c>
       <c r="T59">
-        <v>1.008021840634897</v>
+        <v>1.027510082995704</v>
       </c>
       <c r="U59">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V59">
         <v>0.35</v>
       </c>
       <c r="W59">
-        <v>0.04927000000000001</v>
+        <v>0.0585</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.013461172325923</v>
+        <v>1.666544126657353</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07672843298244733</v>
+        <v>0.0767519593118845</v>
       </c>
       <c r="C60">
-        <v>85.39228242858979</v>
+        <v>82.94522268477041</v>
       </c>
       <c r="D60">
-        <v>220.0122824285898</v>
+        <v>219.9102226847704</v>
       </c>
       <c r="E60">
-        <v>109.51</v>
+        <v>111.855</v>
       </c>
       <c r="F60">
-        <v>136.01</v>
+        <v>138.355</v>
       </c>
       <c r="G60">
         <v>1.39</v>
@@ -6207,28 +6207,28 @@
         <v>20.4</v>
       </c>
       <c r="M60">
-        <v>12.2409</v>
+        <v>12.45195</v>
       </c>
       <c r="N60">
-        <v>8.1591</v>
+        <v>7.94805</v>
       </c>
       <c r="O60">
-        <v>2.855685</v>
+        <v>2.7818175</v>
       </c>
       <c r="P60">
-        <v>5.303415000000001</v>
+        <v>5.1662325</v>
       </c>
       <c r="Q60">
-        <v>8.203415000000003</v>
+        <v>8.066232500000002</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1019010309105889</v>
+        <v>0.1030169739314256</v>
       </c>
       <c r="T60">
-        <v>1.027510082995704</v>
+        <v>1.04794897132533</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.666544126657354</v>
+        <v>1.638297616036043</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.0767519593118845</v>
+        <v>0.07677548564132169</v>
       </c>
       <c r="C61">
-        <v>82.94522268477041</v>
+        <v>80.49825758440949</v>
       </c>
       <c r="D61">
-        <v>219.9102226847704</v>
+        <v>219.8082575844095</v>
       </c>
       <c r="E61">
-        <v>111.855</v>
+        <v>114.2</v>
       </c>
       <c r="F61">
-        <v>138.355</v>
+        <v>140.7</v>
       </c>
       <c r="G61">
         <v>1.39</v>
@@ -6289,28 +6289,28 @@
         <v>20.4</v>
       </c>
       <c r="M61">
-        <v>12.45195</v>
+        <v>12.663</v>
       </c>
       <c r="N61">
-        <v>7.94805</v>
+        <v>7.737</v>
       </c>
       <c r="O61">
-        <v>2.7818175</v>
+        <v>2.70795</v>
       </c>
       <c r="P61">
-        <v>5.1662325</v>
+        <v>5.02905</v>
       </c>
       <c r="Q61">
-        <v>8.066232500000002</v>
+        <v>7.929050000000002</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1030169739314256</v>
+        <v>0.1041887141033042</v>
       </c>
       <c r="T61">
-        <v>1.04794897132533</v>
+        <v>1.069409804071438</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.638297616036043</v>
+        <v>1.610992655768775</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07677548564132169</v>
+        <v>0.07679901197075886</v>
       </c>
       <c r="C62">
-        <v>80.49825758440949</v>
+        <v>78.05138699591907</v>
       </c>
       <c r="D62">
-        <v>219.8082575844095</v>
+        <v>219.7063869959191</v>
       </c>
       <c r="E62">
-        <v>114.2</v>
+        <v>116.545</v>
       </c>
       <c r="F62">
-        <v>140.7</v>
+        <v>143.045</v>
       </c>
       <c r="G62">
         <v>1.39</v>
@@ -6371,28 +6371,28 @@
         <v>20.4</v>
       </c>
       <c r="M62">
-        <v>12.663</v>
+        <v>12.87405</v>
       </c>
       <c r="N62">
-        <v>7.737</v>
+        <v>7.52595</v>
       </c>
       <c r="O62">
-        <v>2.70795</v>
+        <v>2.6340825</v>
       </c>
       <c r="P62">
-        <v>5.02905</v>
+        <v>4.8918675</v>
       </c>
       <c r="Q62">
-        <v>7.929050000000002</v>
+        <v>7.791867500000002</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1041887141033042</v>
+        <v>0.1054205435147663</v>
       </c>
       <c r="T62">
-        <v>1.069409804071438</v>
+        <v>1.091971192342988</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.610992655768775</v>
+        <v>1.584582940100435</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07679901197075886</v>
+        <v>0.07682253830019606</v>
       </c>
       <c r="C63">
-        <v>78.05138699591907</v>
+        <v>75.6046107879547</v>
       </c>
       <c r="D63">
-        <v>219.7063869959191</v>
+        <v>219.6046107879547</v>
       </c>
       <c r="E63">
-        <v>116.545</v>
+        <v>118.89</v>
       </c>
       <c r="F63">
-        <v>143.045</v>
+        <v>145.39</v>
       </c>
       <c r="G63">
         <v>1.39</v>
@@ -6453,28 +6453,28 @@
         <v>20.4</v>
       </c>
       <c r="M63">
-        <v>12.87405</v>
+        <v>13.0851</v>
       </c>
       <c r="N63">
-        <v>7.52595</v>
+        <v>7.3149</v>
       </c>
       <c r="O63">
-        <v>2.6340825</v>
+        <v>2.560215</v>
       </c>
       <c r="P63">
-        <v>4.8918675</v>
+        <v>4.754685</v>
       </c>
       <c r="Q63">
-        <v>7.791867500000002</v>
+        <v>7.654685000000002</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1054205435147663</v>
+        <v>0.1067172060531475</v>
       </c>
       <c r="T63">
-        <v>1.091971192342988</v>
+        <v>1.115720022102514</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.584582940100435</v>
+        <v>1.559025150743976</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07682253830019606</v>
+        <v>0.07684606462963324</v>
       </c>
       <c r="C64">
-        <v>75.6046107879547</v>
+        <v>73.15792882941543</v>
       </c>
       <c r="D64">
-        <v>219.6046107879547</v>
+        <v>219.5029288294155</v>
       </c>
       <c r="E64">
-        <v>118.89</v>
+        <v>121.235</v>
       </c>
       <c r="F64">
-        <v>145.39</v>
+        <v>147.735</v>
       </c>
       <c r="G64">
         <v>1.39</v>
@@ -6535,28 +6535,28 @@
         <v>20.4</v>
       </c>
       <c r="M64">
-        <v>13.0851</v>
+        <v>13.29615</v>
       </c>
       <c r="N64">
-        <v>7.3149</v>
+        <v>7.103849999999998</v>
       </c>
       <c r="O64">
-        <v>2.560215</v>
+        <v>2.486347499999999</v>
       </c>
       <c r="P64">
-        <v>4.754685</v>
+        <v>4.617502499999999</v>
       </c>
       <c r="Q64">
-        <v>7.654685000000002</v>
+        <v>7.517502500000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1067172060531475</v>
+        <v>0.1080839584584682</v>
       </c>
       <c r="T64">
-        <v>1.115720022102514</v>
+        <v>1.140752572389581</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.559025150743976</v>
+        <v>1.534278719779786</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07684606462963324</v>
+        <v>0.07686959095907042</v>
       </c>
       <c r="C65">
-        <v>73.15792882941543</v>
+        <v>70.71134098944299</v>
       </c>
       <c r="D65">
-        <v>219.5029288294155</v>
+        <v>219.401340989443</v>
       </c>
       <c r="E65">
-        <v>121.235</v>
+        <v>123.58</v>
       </c>
       <c r="F65">
-        <v>147.735</v>
+        <v>150.08</v>
       </c>
       <c r="G65">
         <v>1.39</v>
@@ -6617,28 +6617,28 @@
         <v>20.4</v>
       </c>
       <c r="M65">
-        <v>13.29615</v>
+        <v>13.5072</v>
       </c>
       <c r="N65">
-        <v>7.103849999999998</v>
+        <v>6.892799999999998</v>
       </c>
       <c r="O65">
-        <v>2.486347499999999</v>
+        <v>2.412479999999999</v>
       </c>
       <c r="P65">
-        <v>4.617502499999999</v>
+        <v>4.480319999999999</v>
       </c>
       <c r="Q65">
-        <v>7.517502500000001</v>
+        <v>7.380320000000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1080839584584682</v>
+        <v>0.1095266415529734</v>
       </c>
       <c r="T65">
-        <v>1.140752572389581</v>
+        <v>1.167175819914819</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.534278719779786</v>
+        <v>1.510305614783227</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07686959095907042</v>
+        <v>0.104434300361936</v>
       </c>
       <c r="C66">
-        <v>70.71134098944299</v>
+        <v>-8.774570545619241</v>
       </c>
       <c r="D66">
-        <v>219.401340989443</v>
+        <v>142.2604294543808</v>
       </c>
       <c r="E66">
-        <v>123.58</v>
+        <v>125.925</v>
       </c>
       <c r="F66">
-        <v>150.08</v>
+        <v>152.425</v>
       </c>
       <c r="G66">
         <v>1.39</v>
@@ -6699,45 +6699,45 @@
         <v>20.4</v>
       </c>
       <c r="M66">
-        <v>13.5072</v>
+        <v>22.37599000000001</v>
       </c>
       <c r="N66">
-        <v>6.892799999999998</v>
+        <v>-1.975990000000007</v>
       </c>
       <c r="O66">
-        <v>2.412479999999999</v>
+        <v>-0.6915965000000023</v>
       </c>
       <c r="P66">
-        <v>4.480319999999999</v>
+        <v>-1.284393500000004</v>
       </c>
       <c r="Q66">
-        <v>7.380320000000001</v>
+        <v>1.615606499999998</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1095266415529734</v>
+        <v>0.1127487473027595</v>
       </c>
       <c r="T66">
-        <v>1.167175819914819</v>
+        <v>1.226189818278952</v>
       </c>
       <c r="U66">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.35</v>
+        <v>0.3190920267661899</v>
       </c>
       <c r="W66">
-        <v>0.0585</v>
+        <v>0.09995729047072334</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y66">
-        <v>1.510305614783227</v>
+        <v>0.9116915050462568</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.104434300361936</v>
+        <v>0.105444300361936</v>
       </c>
       <c r="C67">
-        <v>-8.774570545619241</v>
+        <v>-12.92898611433233</v>
       </c>
       <c r="D67">
-        <v>142.2604294543808</v>
+        <v>140.4510138856677</v>
       </c>
       <c r="E67">
-        <v>125.925</v>
+        <v>128.27</v>
       </c>
       <c r="F67">
-        <v>152.425</v>
+        <v>154.77</v>
       </c>
       <c r="G67">
         <v>1.39</v>
@@ -6781,37 +6781,37 @@
         <v>20.4</v>
       </c>
       <c r="M67">
-        <v>22.37599000000001</v>
+        <v>22.720236</v>
       </c>
       <c r="N67">
-        <v>-1.975990000000007</v>
+        <v>-2.320236000000005</v>
       </c>
       <c r="O67">
-        <v>-0.6915965000000023</v>
+        <v>-0.8120826000000017</v>
       </c>
       <c r="P67">
-        <v>-1.284393500000004</v>
+        <v>-1.508153400000003</v>
       </c>
       <c r="Q67">
-        <v>1.615606499999998</v>
+        <v>1.391846599999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1127487473027595</v>
+        <v>0.1147178281057818</v>
       </c>
       <c r="T67">
-        <v>1.226189818278952</v>
+        <v>1.262254224698921</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.3190920267661899</v>
+        <v>0.3142572990879143</v>
       </c>
       <c r="W67">
-        <v>0.09995729047072334</v>
+        <v>0.1006670284938942</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.9116915050462568</v>
+        <v>0.8978779973940409</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.105444300361936</v>
+        <v>0.106454300361936</v>
       </c>
       <c r="C68">
-        <v>-12.92898611433233</v>
+        <v>-17.03795171813738</v>
       </c>
       <c r="D68">
-        <v>140.4510138856677</v>
+        <v>138.6870482818626</v>
       </c>
       <c r="E68">
-        <v>128.27</v>
+        <v>130.615</v>
       </c>
       <c r="F68">
-        <v>154.77</v>
+        <v>157.115</v>
       </c>
       <c r="G68">
         <v>1.39</v>
@@ -6863,37 +6863,37 @@
         <v>20.4</v>
       </c>
       <c r="M68">
-        <v>22.720236</v>
+        <v>23.06448200000001</v>
       </c>
       <c r="N68">
-        <v>-2.320236000000005</v>
+        <v>-2.664482000000007</v>
       </c>
       <c r="O68">
-        <v>-0.8120826000000017</v>
+        <v>-0.9325687000000022</v>
       </c>
       <c r="P68">
-        <v>-1.508153400000003</v>
+        <v>-1.731913300000004</v>
       </c>
       <c r="Q68">
-        <v>1.391846599999999</v>
+        <v>1.168086699999998</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1147178281057818</v>
+        <v>0.1168062471392904</v>
       </c>
       <c r="T68">
-        <v>1.262254224698921</v>
+        <v>1.300504352720101</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.3142572990879143</v>
+        <v>0.3095668916388409</v>
       </c>
       <c r="W68">
-        <v>0.1006670284938942</v>
+        <v>0.1013555803074181</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8978779973940409</v>
+        <v>0.8844768332538313</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.106454300361936</v>
+        <v>0.107464300361936</v>
       </c>
       <c r="C69">
-        <v>-17.03795171813738</v>
+        <v>-21.10315857497255</v>
       </c>
       <c r="D69">
-        <v>138.6870482818626</v>
+        <v>136.9668414250275</v>
       </c>
       <c r="E69">
-        <v>130.615</v>
+        <v>132.96</v>
       </c>
       <c r="F69">
-        <v>157.115</v>
+        <v>159.46</v>
       </c>
       <c r="G69">
         <v>1.39</v>
@@ -6945,37 +6945,37 @@
         <v>20.4</v>
       </c>
       <c r="M69">
-        <v>23.06448200000001</v>
+        <v>23.408728</v>
       </c>
       <c r="N69">
-        <v>-2.664482000000007</v>
+        <v>-3.008728000000005</v>
       </c>
       <c r="O69">
-        <v>-0.9325687000000022</v>
+        <v>-1.053054800000002</v>
       </c>
       <c r="P69">
-        <v>-1.731913300000004</v>
+        <v>-1.955673200000003</v>
       </c>
       <c r="Q69">
-        <v>1.168086699999998</v>
+        <v>0.9443267999999989</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1168062471392904</v>
+        <v>0.1190251923623932</v>
       </c>
       <c r="T69">
-        <v>1.300504352720101</v>
+        <v>1.341145113742604</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.3095668916388409</v>
+        <v>0.3050144373500345</v>
       </c>
       <c r="W69">
-        <v>0.1013555803074181</v>
+        <v>0.1020238805970149</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8844768332538313</v>
+        <v>0.8714698210000986</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.107464300361936</v>
+        <v>0.108474300361936</v>
       </c>
       <c r="C70">
-        <v>-21.10315857497255</v>
+        <v>-25.12621502259444</v>
       </c>
       <c r="D70">
-        <v>136.9668414250275</v>
+        <v>135.2887849774056</v>
       </c>
       <c r="E70">
-        <v>132.96</v>
+        <v>135.305</v>
       </c>
       <c r="F70">
-        <v>159.46</v>
+        <v>161.805</v>
       </c>
       <c r="G70">
         <v>1.39</v>
@@ -7027,37 +7027,37 @@
         <v>20.4</v>
       </c>
       <c r="M70">
-        <v>23.408728</v>
+        <v>23.752974</v>
       </c>
       <c r="N70">
-        <v>-3.008728000000005</v>
+        <v>-3.352974000000003</v>
       </c>
       <c r="O70">
-        <v>-1.053054800000002</v>
+        <v>-1.173540900000001</v>
       </c>
       <c r="P70">
-        <v>-1.955673200000003</v>
+        <v>-2.179433100000002</v>
       </c>
       <c r="Q70">
-        <v>0.9443267999999989</v>
+        <v>0.7205668999999997</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1190251923623932</v>
+        <v>0.1213872953418252</v>
       </c>
       <c r="T70">
-        <v>1.341145113742604</v>
+        <v>1.384407859347204</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.3050144373500345</v>
+        <v>0.300593938258005</v>
       </c>
       <c r="W70">
-        <v>0.1020238805970149</v>
+        <v>0.1026728098637249</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8714698210000986</v>
+        <v>0.8588398235943001</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.108474300361936</v>
+        <v>0.109484300361936</v>
       </c>
       <c r="C71">
-        <v>-25.12621502259444</v>
+        <v>-29.10865153418388</v>
       </c>
       <c r="D71">
-        <v>135.2887849774056</v>
+        <v>133.6513484658161</v>
       </c>
       <c r="E71">
-        <v>135.305</v>
+        <v>137.65</v>
       </c>
       <c r="F71">
-        <v>161.805</v>
+        <v>164.15</v>
       </c>
       <c r="G71">
         <v>1.39</v>
@@ -7109,37 +7109,37 @@
         <v>20.4</v>
       </c>
       <c r="M71">
-        <v>23.752974</v>
+        <v>24.09722</v>
       </c>
       <c r="N71">
-        <v>-3.352974000000003</v>
+        <v>-3.697220000000005</v>
       </c>
       <c r="O71">
-        <v>-1.173540900000001</v>
+        <v>-1.294027000000002</v>
       </c>
       <c r="P71">
-        <v>-2.179433100000002</v>
+        <v>-2.403193000000003</v>
       </c>
       <c r="Q71">
-        <v>0.7205668999999997</v>
+        <v>0.4968069999999987</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1213872953418252</v>
+        <v>0.1239068718532194</v>
       </c>
       <c r="T71">
-        <v>1.384407859347204</v>
+        <v>1.430554787992111</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.300593938258005</v>
+        <v>0.2962997391400335</v>
       </c>
       <c r="W71">
-        <v>0.1026728098637249</v>
+        <v>0.1033031982942431</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8588398235943001</v>
+        <v>0.8465706832572386</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.109484300361936</v>
+        <v>0.110494300361936</v>
       </c>
       <c r="C72">
-        <v>-29.10865153418388</v>
+        <v>-33.05192537407569</v>
       </c>
       <c r="D72">
-        <v>133.6513484658161</v>
+        <v>132.0530746259243</v>
       </c>
       <c r="E72">
-        <v>137.65</v>
+        <v>139.995</v>
       </c>
       <c r="F72">
-        <v>164.15</v>
+        <v>166.495</v>
       </c>
       <c r="G72">
         <v>1.39</v>
@@ -7191,37 +7191,37 @@
         <v>20.4</v>
       </c>
       <c r="M72">
-        <v>24.09722</v>
+        <v>24.441466</v>
       </c>
       <c r="N72">
-        <v>-3.697220000000005</v>
+        <v>-4.041466000000003</v>
       </c>
       <c r="O72">
-        <v>-1.294027000000002</v>
+        <v>-1.414513100000001</v>
       </c>
       <c r="P72">
-        <v>-2.403193000000003</v>
+        <v>-2.626952900000002</v>
       </c>
       <c r="Q72">
-        <v>0.4968069999999987</v>
+        <v>0.2730470999999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1239068718532194</v>
+        <v>0.1266002122619511</v>
       </c>
       <c r="T72">
-        <v>1.430554787992111</v>
+        <v>1.479884263440115</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.2962997391400335</v>
+        <v>0.2921265033774978</v>
       </c>
       <c r="W72">
-        <v>0.1033031982942431</v>
+        <v>0.1039158293041833</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8465706832572386</v>
+        <v>0.8346471525071367</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.110494300361936</v>
+        <v>0.111504300361936</v>
       </c>
       <c r="C73">
-        <v>-33.05192537407569</v>
+        <v>-36.95742492338192</v>
       </c>
       <c r="D73">
-        <v>132.0530746259243</v>
+        <v>130.4925750766181</v>
       </c>
       <c r="E73">
-        <v>139.995</v>
+        <v>142.34</v>
       </c>
       <c r="F73">
-        <v>166.495</v>
+        <v>168.84</v>
       </c>
       <c r="G73">
         <v>1.39</v>
@@ -7273,37 +7273,37 @@
         <v>20.4</v>
       </c>
       <c r="M73">
-        <v>24.441466</v>
+        <v>24.785712</v>
       </c>
       <c r="N73">
-        <v>-4.041466000000003</v>
+        <v>-4.385712000000005</v>
       </c>
       <c r="O73">
-        <v>-1.414513100000001</v>
+        <v>-1.534999200000002</v>
       </c>
       <c r="P73">
-        <v>-2.626952900000002</v>
+        <v>-2.850712800000004</v>
       </c>
       <c r="Q73">
-        <v>0.2730470999999999</v>
+        <v>0.04928719999999842</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1266002122619511</v>
+        <v>0.1294859341284494</v>
       </c>
       <c r="T73">
-        <v>1.479884263440114</v>
+        <v>1.532737272848689</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.2921265033774978</v>
+        <v>0.2880691908305881</v>
       </c>
       <c r="W73">
-        <v>0.1039158293041833</v>
+        <v>0.1045114427860697</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8346471525071367</v>
+        <v>0.8230548309445376</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.111504300361936</v>
+        <v>0.112514300361936</v>
       </c>
       <c r="C74">
-        <v>-36.95742492338192</v>
+        <v>-40.82647370249634</v>
       </c>
       <c r="D74">
-        <v>130.4925750766181</v>
+        <v>128.9685262975037</v>
       </c>
       <c r="E74">
-        <v>142.34</v>
+        <v>144.685</v>
       </c>
       <c r="F74">
-        <v>168.84</v>
+        <v>171.185</v>
       </c>
       <c r="G74">
         <v>1.39</v>
@@ -7355,37 +7355,37 @@
         <v>20.4</v>
       </c>
       <c r="M74">
-        <v>24.785712</v>
+        <v>25.129958</v>
       </c>
       <c r="N74">
-        <v>-4.385712000000005</v>
+        <v>-4.729958000000003</v>
       </c>
       <c r="O74">
-        <v>-1.534999200000002</v>
+        <v>-1.655485300000001</v>
       </c>
       <c r="P74">
-        <v>-2.850712800000004</v>
+        <v>-3.074472700000002</v>
       </c>
       <c r="Q74">
-        <v>0.04928719999999842</v>
+        <v>-0.1744726999999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1294859341284494</v>
+        <v>0.1325854131702438</v>
       </c>
       <c r="T74">
-        <v>1.532737272848689</v>
+        <v>1.589505319991234</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.2880691908305881</v>
+        <v>0.284123037531539</v>
       </c>
       <c r="W74">
-        <v>0.1045114427860697</v>
+        <v>0.1050907380903701</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8230548309445376</v>
+        <v>0.8117801072329686</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.112514300361936</v>
+        <v>0.113524300361936</v>
       </c>
       <c r="C75">
-        <v>-40.82647370249634</v>
+        <v>-44.66033411497509</v>
       </c>
       <c r="D75">
-        <v>128.9685262975037</v>
+        <v>127.4796658850249</v>
       </c>
       <c r="E75">
-        <v>144.685</v>
+        <v>147.03</v>
       </c>
       <c r="F75">
-        <v>171.185</v>
+        <v>173.53</v>
       </c>
       <c r="G75">
         <v>1.39</v>
@@ -7437,37 +7437,37 @@
         <v>20.4</v>
       </c>
       <c r="M75">
-        <v>25.129958</v>
+        <v>25.474204</v>
       </c>
       <c r="N75">
-        <v>-4.729958000000003</v>
+        <v>-5.074204000000005</v>
       </c>
       <c r="O75">
-        <v>-1.655485300000001</v>
+        <v>-1.775971400000002</v>
       </c>
       <c r="P75">
-        <v>-3.074472700000002</v>
+        <v>-3.298232600000004</v>
       </c>
       <c r="Q75">
-        <v>-0.1744726999999999</v>
+        <v>-0.3982326000000014</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1325854131702438</v>
+        <v>0.1359233136767916</v>
       </c>
       <c r="T75">
-        <v>1.589505319991234</v>
+        <v>1.650640139990897</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.284123037531539</v>
+        <v>0.280283537024356</v>
       </c>
       <c r="W75">
-        <v>0.1050907380903701</v>
+        <v>0.1056543767648246</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8117801072329686</v>
+        <v>0.8008101057838743</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.113524300361936</v>
+        <v>0.1566833023202664</v>
       </c>
       <c r="C76">
-        <v>-44.66033411497509</v>
+        <v>-89.11784087885607</v>
       </c>
       <c r="D76">
-        <v>127.4796658850249</v>
+        <v>85.36715912114393</v>
       </c>
       <c r="E76">
-        <v>147.03</v>
+        <v>149.375</v>
       </c>
       <c r="F76">
-        <v>173.53</v>
+        <v>175.875</v>
       </c>
       <c r="G76">
         <v>1.39</v>
@@ -7519,45 +7519,45 @@
         <v>20.4</v>
       </c>
       <c r="M76">
-        <v>25.474204</v>
+        <v>35.3157</v>
       </c>
       <c r="N76">
-        <v>-5.074204000000005</v>
+        <v>-14.9157</v>
       </c>
       <c r="O76">
-        <v>-1.775971400000002</v>
+        <v>-5.220495</v>
       </c>
       <c r="P76">
-        <v>-3.298232600000004</v>
+        <v>-9.695205000000001</v>
       </c>
       <c r="Q76">
-        <v>-0.3982326000000014</v>
+        <v>-6.795204999999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1359233136767916</v>
+        <v>0.1461242540571849</v>
       </c>
       <c r="T76">
-        <v>1.650640139990897</v>
+        <v>1.837473945480089</v>
       </c>
       <c r="U76">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.280283537024356</v>
+        <v>0.2021763691502646</v>
       </c>
       <c r="W76">
-        <v>0.1056543767648246</v>
+        <v>0.1602029850746269</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.8008101057838743</v>
+        <v>0.5776467690007561</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1566833023202664</v>
+        <v>0.1582333023202664</v>
       </c>
       <c r="C77">
-        <v>-89.11784087885607</v>
+        <v>-92.46376043358735</v>
       </c>
       <c r="D77">
-        <v>85.36715912114393</v>
+        <v>84.36623956641264</v>
       </c>
       <c r="E77">
-        <v>149.375</v>
+        <v>151.72</v>
       </c>
       <c r="F77">
-        <v>175.875</v>
+        <v>178.22</v>
       </c>
       <c r="G77">
         <v>1.39</v>
@@ -7601,37 +7601,37 @@
         <v>20.4</v>
       </c>
       <c r="M77">
-        <v>35.3157</v>
+        <v>35.786576</v>
       </c>
       <c r="N77">
-        <v>-14.9157</v>
+        <v>-15.38657600000001</v>
       </c>
       <c r="O77">
-        <v>-5.220495</v>
+        <v>-5.385301600000002</v>
       </c>
       <c r="P77">
-        <v>-9.695205000000001</v>
+        <v>-10.0012744</v>
       </c>
       <c r="Q77">
-        <v>-6.795204999999999</v>
+        <v>-7.101274400000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1461242540571849</v>
+        <v>0.1503044313095676</v>
       </c>
       <c r="T77">
-        <v>1.837473945480089</v>
+        <v>1.914035359875093</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.2021763691502646</v>
+        <v>0.1995161537667084</v>
       </c>
       <c r="W77">
-        <v>0.1602029850746269</v>
+        <v>0.1607371563236449</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5776467690007561</v>
+        <v>0.570046153619167</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1582333023202664</v>
+        <v>0.1597833023202664</v>
       </c>
       <c r="C78">
-        <v>-92.46376043358735</v>
+        <v>-95.78648067740646</v>
       </c>
       <c r="D78">
-        <v>84.36623956641264</v>
+        <v>83.38851932259354</v>
       </c>
       <c r="E78">
-        <v>151.72</v>
+        <v>154.065</v>
       </c>
       <c r="F78">
-        <v>178.22</v>
+        <v>180.565</v>
       </c>
       <c r="G78">
         <v>1.39</v>
@@ -7683,37 +7683,37 @@
         <v>20.4</v>
       </c>
       <c r="M78">
-        <v>35.786576</v>
+        <v>36.257452</v>
       </c>
       <c r="N78">
-        <v>-15.38657600000001</v>
+        <v>-15.857452</v>
       </c>
       <c r="O78">
-        <v>-5.385301600000002</v>
+        <v>-5.5501082</v>
       </c>
       <c r="P78">
-        <v>-10.0012744</v>
+        <v>-10.3073438</v>
       </c>
       <c r="Q78">
-        <v>-7.101274400000001</v>
+        <v>-7.4073438</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1503044313095676</v>
+        <v>0.1548481022360706</v>
       </c>
       <c r="T78">
-        <v>1.914035359875093</v>
+        <v>1.997254288565314</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1995161537667084</v>
+        <v>0.1969250348866214</v>
       </c>
       <c r="W78">
-        <v>0.1607371563236449</v>
+        <v>0.1612574529947664</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.570046153619167</v>
+        <v>0.5626429568189182</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1597833023202664</v>
+        <v>0.1613333023202664</v>
       </c>
       <c r="C79">
-        <v>-95.78648067740646</v>
+        <v>-99.0867989404106</v>
       </c>
       <c r="D79">
-        <v>83.38851932259354</v>
+        <v>82.43320105958939</v>
       </c>
       <c r="E79">
-        <v>154.065</v>
+        <v>156.41</v>
       </c>
       <c r="F79">
-        <v>180.565</v>
+        <v>182.91</v>
       </c>
       <c r="G79">
         <v>1.39</v>
@@ -7765,37 +7765,37 @@
         <v>20.4</v>
       </c>
       <c r="M79">
-        <v>36.257452</v>
+        <v>36.728328</v>
       </c>
       <c r="N79">
-        <v>-15.857452</v>
+        <v>-16.328328</v>
       </c>
       <c r="O79">
-        <v>-5.5501082</v>
+        <v>-5.714914799999999</v>
       </c>
       <c r="P79">
-        <v>-10.3073438</v>
+        <v>-10.6134132</v>
       </c>
       <c r="Q79">
-        <v>-7.4073438</v>
+        <v>-7.713413199999998</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1548481022360706</v>
+        <v>0.159804834155892</v>
       </c>
       <c r="T79">
-        <v>1.997254288565314</v>
+        <v>2.088038574409193</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1969250348866214</v>
+        <v>0.1944003549521775</v>
       </c>
       <c r="W79">
-        <v>0.1612574529947664</v>
+        <v>0.1617644087256028</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5626429568189182</v>
+        <v>0.5554295855776501</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1613333023202664</v>
+        <v>0.1628833023202664</v>
       </c>
       <c r="C80">
-        <v>-99.0867989404106</v>
+        <v>-102.365476428943</v>
       </c>
       <c r="D80">
-        <v>82.43320105958939</v>
+        <v>81.49952357105695</v>
       </c>
       <c r="E80">
-        <v>156.41</v>
+        <v>158.755</v>
       </c>
       <c r="F80">
-        <v>182.91</v>
+        <v>185.255</v>
       </c>
       <c r="G80">
         <v>1.39</v>
@@ -7847,37 +7847,37 @@
         <v>20.4</v>
       </c>
       <c r="M80">
-        <v>36.728328</v>
+        <v>37.199204</v>
       </c>
       <c r="N80">
-        <v>-16.328328</v>
+        <v>-16.799204</v>
       </c>
       <c r="O80">
-        <v>-5.714914799999999</v>
+        <v>-5.879721400000001</v>
       </c>
       <c r="P80">
-        <v>-10.6134132</v>
+        <v>-10.9194826</v>
       </c>
       <c r="Q80">
-        <v>-7.713413199999998</v>
+        <v>-8.0194826</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.159804834155892</v>
+        <v>0.165233635782363</v>
       </c>
       <c r="T80">
-        <v>2.088038574409193</v>
+        <v>2.187468982714392</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1944003549521775</v>
+        <v>0.1919395909654411</v>
       </c>
       <c r="W80">
-        <v>0.1617644087256028</v>
+        <v>0.1622585301341394</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5554295855776501</v>
+        <v>0.5483988313298316</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1628833023202664</v>
+        <v>0.1644333023202664</v>
       </c>
       <c r="C81">
-        <v>-102.365476428943</v>
+        <v>-105.6232402484556</v>
       </c>
       <c r="D81">
-        <v>81.49952357105695</v>
+        <v>80.58675975154442</v>
       </c>
       <c r="E81">
-        <v>158.755</v>
+        <v>161.1</v>
       </c>
       <c r="F81">
-        <v>185.255</v>
+        <v>187.6</v>
       </c>
       <c r="G81">
         <v>1.39</v>
@@ -7929,37 +7929,37 @@
         <v>20.4</v>
       </c>
       <c r="M81">
-        <v>37.199204</v>
+        <v>37.67008000000001</v>
       </c>
       <c r="N81">
-        <v>-16.799204</v>
+        <v>-17.27008000000001</v>
       </c>
       <c r="O81">
-        <v>-5.879721400000001</v>
+        <v>-6.044528000000002</v>
       </c>
       <c r="P81">
-        <v>-10.9194826</v>
+        <v>-11.225552</v>
       </c>
       <c r="Q81">
-        <v>-8.0194826</v>
+        <v>-8.325552000000002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.165233635782363</v>
+        <v>0.1712053175714812</v>
       </c>
       <c r="T81">
-        <v>2.187468982714392</v>
+        <v>2.296842431850112</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1919395909654411</v>
+        <v>0.189540346078373</v>
       </c>
       <c r="W81">
-        <v>0.1622585301341394</v>
+        <v>0.1627402985074627</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5483988313298316</v>
+        <v>0.5415438459382087</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1644333023202664</v>
+        <v>0.1659833023202664</v>
       </c>
       <c r="C82">
-        <v>-105.6232402484556</v>
+        <v>-108.8607852919435</v>
       </c>
       <c r="D82">
-        <v>80.58675975154442</v>
+        <v>79.69421470805648</v>
       </c>
       <c r="E82">
-        <v>161.1</v>
+        <v>163.445</v>
       </c>
       <c r="F82">
-        <v>187.6</v>
+        <v>189.945</v>
       </c>
       <c r="G82">
         <v>1.39</v>
@@ -8011,37 +8011,37 @@
         <v>20.4</v>
       </c>
       <c r="M82">
-        <v>37.67008000000001</v>
+        <v>38.140956</v>
       </c>
       <c r="N82">
-        <v>-17.27008000000001</v>
+        <v>-17.740956</v>
       </c>
       <c r="O82">
-        <v>-6.044528000000002</v>
+        <v>-6.209334600000001</v>
       </c>
       <c r="P82">
-        <v>-11.225552</v>
+        <v>-11.5316214</v>
       </c>
       <c r="Q82">
-        <v>-8.325552000000002</v>
+        <v>-8.6316214</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1712053175714812</v>
+        <v>0.1778055974436644</v>
       </c>
       <c r="T82">
-        <v>2.296842431850112</v>
+        <v>2.417728875631697</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.189540346078373</v>
+        <v>0.1872003418058005</v>
       </c>
       <c r="W82">
-        <v>0.1627402985074627</v>
+        <v>0.1632101713653953</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5415438459382087</v>
+        <v>0.5348581194451444</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1659833023202664</v>
+        <v>0.1675333023202664</v>
       </c>
       <c r="C83">
-        <v>-108.8607852919435</v>
+        <v>-112.0787760042634</v>
       </c>
       <c r="D83">
-        <v>79.69421470805648</v>
+        <v>78.82122399573664</v>
       </c>
       <c r="E83">
-        <v>163.445</v>
+        <v>165.79</v>
       </c>
       <c r="F83">
-        <v>189.945</v>
+        <v>192.29</v>
       </c>
       <c r="G83">
         <v>1.39</v>
@@ -8093,37 +8093,37 @@
         <v>20.4</v>
       </c>
       <c r="M83">
-        <v>38.140956</v>
+        <v>38.61183200000001</v>
       </c>
       <c r="N83">
-        <v>-17.740956</v>
+        <v>-18.21183200000001</v>
       </c>
       <c r="O83">
-        <v>-6.209334600000001</v>
+        <v>-6.374141200000002</v>
       </c>
       <c r="P83">
-        <v>-11.5316214</v>
+        <v>-11.83769080000001</v>
       </c>
       <c r="Q83">
-        <v>-8.6316214</v>
+        <v>-8.937690800000004</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1778055974436644</v>
+        <v>0.1851392417460902</v>
       </c>
       <c r="T83">
-        <v>2.417728875631697</v>
+        <v>2.552047146500125</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1872003418058005</v>
+        <v>0.1849174108081688</v>
       </c>
       <c r="W83">
-        <v>0.1632101713653953</v>
+        <v>0.1636685839097197</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5348581194451444</v>
+        <v>0.528335459451911</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1675333023202664</v>
+        <v>0.1690833023202664</v>
       </c>
       <c r="C84">
-        <v>-112.0787760042634</v>
+        <v>-115.2778480317456</v>
       </c>
       <c r="D84">
-        <v>78.82122399573664</v>
+        <v>77.96715196825441</v>
       </c>
       <c r="E84">
-        <v>165.79</v>
+        <v>168.135</v>
       </c>
       <c r="F84">
-        <v>192.29</v>
+        <v>194.635</v>
       </c>
       <c r="G84">
         <v>1.39</v>
@@ -8175,37 +8175,37 @@
         <v>20.4</v>
       </c>
       <c r="M84">
-        <v>38.61183200000001</v>
+        <v>39.082708</v>
       </c>
       <c r="N84">
-        <v>-18.21183200000001</v>
+        <v>-18.68270800000001</v>
       </c>
       <c r="O84">
-        <v>-6.374141200000002</v>
+        <v>-6.538947800000002</v>
       </c>
       <c r="P84">
-        <v>-11.83769080000001</v>
+        <v>-12.1437602</v>
       </c>
       <c r="Q84">
-        <v>-8.937690800000004</v>
+        <v>-9.243760200000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1851392417460902</v>
+        <v>0.1933356677311544</v>
       </c>
       <c r="T84">
-        <v>2.552047146500125</v>
+        <v>2.702167566882485</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1849174108081688</v>
+        <v>0.1826894901960222</v>
       </c>
       <c r="W84">
-        <v>0.1636685839097197</v>
+        <v>0.1641159503686387</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.528335459451911</v>
+        <v>0.5219699719886348</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1690833023202664</v>
+        <v>0.1706333023202664</v>
       </c>
       <c r="C85">
-        <v>-115.2778480317456</v>
+        <v>-118.4586097657107</v>
       </c>
       <c r="D85">
-        <v>77.96715196825441</v>
+        <v>77.13139023428934</v>
       </c>
       <c r="E85">
-        <v>168.135</v>
+        <v>170.48</v>
       </c>
       <c r="F85">
-        <v>194.635</v>
+        <v>196.98</v>
       </c>
       <c r="G85">
         <v>1.39</v>
@@ -8257,37 +8257,37 @@
         <v>20.4</v>
       </c>
       <c r="M85">
-        <v>39.082708</v>
+        <v>39.55358400000001</v>
       </c>
       <c r="N85">
-        <v>-18.68270800000001</v>
+        <v>-19.15358400000001</v>
       </c>
       <c r="O85">
-        <v>-6.538947800000002</v>
+        <v>-6.703754400000003</v>
       </c>
       <c r="P85">
-        <v>-12.1437602</v>
+        <v>-12.44982960000001</v>
       </c>
       <c r="Q85">
-        <v>-9.243760200000001</v>
+        <v>-9.549829600000004</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1933356677311544</v>
+        <v>0.2025566469643515</v>
       </c>
       <c r="T85">
-        <v>2.702167566882485</v>
+        <v>2.871053039812641</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1826894901960222</v>
+        <v>0.1805146153127362</v>
       </c>
       <c r="W85">
-        <v>0.1641159503686387</v>
+        <v>0.1645526652452026</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5219699719886348</v>
+        <v>0.515756043750675</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1706333023202664</v>
+        <v>0.1721833023202664</v>
       </c>
       <c r="C86">
-        <v>-118.4586097657106</v>
+        <v>-121.6216437877639</v>
       </c>
       <c r="D86">
-        <v>77.13139023428937</v>
+        <v>76.31335621223609</v>
       </c>
       <c r="E86">
-        <v>170.48</v>
+        <v>172.825</v>
       </c>
       <c r="F86">
-        <v>196.98</v>
+        <v>199.325</v>
       </c>
       <c r="G86">
         <v>1.39</v>
@@ -8339,37 +8339,37 @@
         <v>20.4</v>
       </c>
       <c r="M86">
-        <v>39.553584</v>
+        <v>40.02446</v>
       </c>
       <c r="N86">
-        <v>-19.153584</v>
+        <v>-19.62446</v>
       </c>
       <c r="O86">
-        <v>-6.7037544</v>
+        <v>-6.868561</v>
       </c>
       <c r="P86">
-        <v>-12.4498296</v>
+        <v>-12.755899</v>
       </c>
       <c r="Q86">
-        <v>-9.549829599999999</v>
+        <v>-9.855898999999997</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2025566469643514</v>
+        <v>0.2130070900953082</v>
       </c>
       <c r="T86">
-        <v>2.871053039812639</v>
+        <v>3.062456575800149</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1805146153127362</v>
+        <v>0.1783909139561158</v>
       </c>
       <c r="W86">
-        <v>0.1645526652452026</v>
+        <v>0.1649791044776119</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.515756043750675</v>
+        <v>0.5096883255889024</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1721833023202664</v>
+        <v>0.1737333023202664</v>
       </c>
       <c r="C87">
-        <v>-121.6216437877639</v>
+        <v>-124.7675082240859</v>
       </c>
       <c r="D87">
-        <v>76.31335621223609</v>
+        <v>75.51249177591411</v>
       </c>
       <c r="E87">
-        <v>172.825</v>
+        <v>175.17</v>
       </c>
       <c r="F87">
-        <v>199.325</v>
+        <v>201.67</v>
       </c>
       <c r="G87">
         <v>1.39</v>
@@ -8421,37 +8421,37 @@
         <v>20.4</v>
       </c>
       <c r="M87">
-        <v>40.02446</v>
+        <v>40.495336</v>
       </c>
       <c r="N87">
-        <v>-19.62446</v>
+        <v>-20.095336</v>
       </c>
       <c r="O87">
-        <v>-6.868561</v>
+        <v>-7.033367600000001</v>
       </c>
       <c r="P87">
-        <v>-12.755899</v>
+        <v>-13.0619684</v>
       </c>
       <c r="Q87">
-        <v>-9.855898999999997</v>
+        <v>-10.1619684</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2130070900953082</v>
+        <v>0.2249504536735445</v>
       </c>
       <c r="T87">
-        <v>3.062456575800149</v>
+        <v>3.281203474071587</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1783909139561158</v>
+        <v>0.1763166010031377</v>
       </c>
       <c r="W87">
-        <v>0.1649791044776119</v>
+        <v>0.16539562651857</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5096883255889024</v>
+        <v>0.5037617171518221</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1737333023202664</v>
+        <v>0.2063986945281876</v>
       </c>
       <c r="C88">
-        <v>-124.7675082240859</v>
+        <v>-140.7885181195884</v>
       </c>
       <c r="D88">
-        <v>75.51249177591411</v>
+        <v>61.83648188041159</v>
       </c>
       <c r="E88">
-        <v>175.17</v>
+        <v>177.515</v>
       </c>
       <c r="F88">
-        <v>201.67</v>
+        <v>204.015</v>
       </c>
       <c r="G88">
         <v>1.39</v>
@@ -8503,45 +8503,45 @@
         <v>20.4</v>
       </c>
       <c r="M88">
-        <v>40.495336</v>
+        <v>48.106737</v>
       </c>
       <c r="N88">
-        <v>-20.095336</v>
+        <v>-27.706737</v>
       </c>
       <c r="O88">
-        <v>-7.033367600000001</v>
+        <v>-9.697357949999999</v>
       </c>
       <c r="P88">
-        <v>-13.0619684</v>
+        <v>-18.00937905</v>
       </c>
       <c r="Q88">
-        <v>-10.1619684</v>
+        <v>-15.10937905</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2249504536735445</v>
+        <v>0.2438496594016722</v>
       </c>
       <c r="T88">
-        <v>3.281203474071587</v>
+        <v>3.627349064109151</v>
       </c>
       <c r="U88">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1763166010031377</v>
+        <v>0.1484199603893317</v>
       </c>
       <c r="W88">
-        <v>0.16539562651857</v>
+        <v>0.2008025733401956</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.5037617171518221</v>
+        <v>0.424057029683805</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2063986945281876</v>
+        <v>0.2082986945281876</v>
       </c>
       <c r="C89">
-        <v>-140.7885181195884</v>
+        <v>-143.7781325684255</v>
       </c>
       <c r="D89">
-        <v>61.83648188041159</v>
+        <v>61.19186743157447</v>
       </c>
       <c r="E89">
-        <v>177.515</v>
+        <v>179.86</v>
       </c>
       <c r="F89">
-        <v>204.015</v>
+        <v>206.36</v>
       </c>
       <c r="G89">
         <v>1.39</v>
@@ -8585,37 +8585,37 @@
         <v>20.4</v>
       </c>
       <c r="M89">
-        <v>48.106737</v>
+        <v>48.659688</v>
       </c>
       <c r="N89">
-        <v>-27.706737</v>
+        <v>-28.259688</v>
       </c>
       <c r="O89">
-        <v>-9.697357949999999</v>
+        <v>-9.890890800000001</v>
       </c>
       <c r="P89">
-        <v>-18.00937905</v>
+        <v>-18.3687972</v>
       </c>
       <c r="Q89">
-        <v>-15.10937905</v>
+        <v>-15.4687972</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2438496594016722</v>
+        <v>0.2603537976851449</v>
       </c>
       <c r="T89">
-        <v>3.627349064109151</v>
+        <v>3.929628152784914</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1484199603893317</v>
+        <v>0.146733369930362</v>
       </c>
       <c r="W89">
-        <v>0.2008025733401956</v>
+        <v>0.2012002713704207</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.424057029683805</v>
+        <v>0.4192381998010344</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2082986945281876</v>
+        <v>0.2101986945281875</v>
       </c>
       <c r="C90">
-        <v>-143.7781325684255</v>
+        <v>-146.7544461050808</v>
       </c>
       <c r="D90">
-        <v>61.19186743157447</v>
+        <v>60.56055389491919</v>
       </c>
       <c r="E90">
-        <v>179.86</v>
+        <v>182.205</v>
       </c>
       <c r="F90">
-        <v>206.36</v>
+        <v>208.705</v>
       </c>
       <c r="G90">
         <v>1.39</v>
@@ -8667,37 +8667,37 @@
         <v>20.4</v>
       </c>
       <c r="M90">
-        <v>48.659688</v>
+        <v>49.212639</v>
       </c>
       <c r="N90">
-        <v>-28.259688</v>
+        <v>-28.812639</v>
       </c>
       <c r="O90">
-        <v>-9.890890800000001</v>
+        <v>-10.08442365</v>
       </c>
       <c r="P90">
-        <v>-18.3687972</v>
+        <v>-18.72821535</v>
       </c>
       <c r="Q90">
-        <v>-15.4687972</v>
+        <v>-15.82821535</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2603537976851449</v>
+        <v>0.2798586883837944</v>
       </c>
       <c r="T90">
-        <v>3.929628152784914</v>
+        <v>4.28686707576536</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.146733369930362</v>
+        <v>0.1450846803805827</v>
       </c>
       <c r="W90">
-        <v>0.2012002713704207</v>
+        <v>0.2015890323662586</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4192381998010344</v>
+        <v>0.4145276582302363</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2101986945281875</v>
+        <v>0.2120986945281875</v>
       </c>
       <c r="C91">
-        <v>-146.7544461050808</v>
+        <v>-149.7178662003013</v>
       </c>
       <c r="D91">
-        <v>60.56055389491919</v>
+        <v>59.94213379969872</v>
       </c>
       <c r="E91">
-        <v>182.205</v>
+        <v>184.55</v>
       </c>
       <c r="F91">
-        <v>208.705</v>
+        <v>211.05</v>
       </c>
       <c r="G91">
         <v>1.39</v>
@@ -8749,37 +8749,37 @@
         <v>20.4</v>
       </c>
       <c r="M91">
-        <v>49.212639</v>
+        <v>49.76559</v>
       </c>
       <c r="N91">
-        <v>-28.812639</v>
+        <v>-29.36559</v>
       </c>
       <c r="O91">
-        <v>-10.08442365</v>
+        <v>-10.2779565</v>
       </c>
       <c r="P91">
-        <v>-18.72821535</v>
+        <v>-19.0876335</v>
       </c>
       <c r="Q91">
-        <v>-15.82821535</v>
+        <v>-16.1876335</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2798586883837944</v>
+        <v>0.3032645572221739</v>
       </c>
       <c r="T91">
-        <v>4.28686707576536</v>
+        <v>4.715553783341898</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1450846803805827</v>
+        <v>0.143472628376354</v>
       </c>
       <c r="W91">
-        <v>0.2015890323662586</v>
+        <v>0.2019691542288557</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4145276582302363</v>
+        <v>0.4099217953610115</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2120986945281875</v>
+        <v>0.2139986945281875</v>
       </c>
       <c r="C92">
-        <v>-149.7178662003013</v>
+        <v>-152.6687838493632</v>
       </c>
       <c r="D92">
-        <v>59.94213379969872</v>
+        <v>59.33621615063679</v>
       </c>
       <c r="E92">
-        <v>184.55</v>
+        <v>186.895</v>
       </c>
       <c r="F92">
-        <v>211.05</v>
+        <v>213.395</v>
       </c>
       <c r="G92">
         <v>1.39</v>
@@ -8831,37 +8831,37 @@
         <v>20.4</v>
       </c>
       <c r="M92">
-        <v>49.76559</v>
+        <v>50.318541</v>
       </c>
       <c r="N92">
-        <v>-29.36559</v>
+        <v>-29.918541</v>
       </c>
       <c r="O92">
-        <v>-10.2779565</v>
+        <v>-10.47148935</v>
       </c>
       <c r="P92">
-        <v>-19.0876335</v>
+        <v>-19.44705165000001</v>
       </c>
       <c r="Q92">
-        <v>-16.1876335</v>
+        <v>-16.54705165</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3032645572221739</v>
+        <v>0.33187173024686</v>
       </c>
       <c r="T92">
-        <v>4.715553783341898</v>
+        <v>5.23950420371322</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.143472628376354</v>
+        <v>0.141896006086504</v>
       </c>
       <c r="W92">
-        <v>0.2019691542288557</v>
+        <v>0.2023409217648024</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4099217953610115</v>
+        <v>0.4054171602471541</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2139986945281875</v>
+        <v>0.2158986945281876</v>
       </c>
       <c r="C93">
-        <v>-152.6687838493632</v>
+        <v>-155.6075743964406</v>
       </c>
       <c r="D93">
-        <v>59.33621615063679</v>
+        <v>58.74242560355945</v>
       </c>
       <c r="E93">
-        <v>186.895</v>
+        <v>189.24</v>
       </c>
       <c r="F93">
-        <v>213.395</v>
+        <v>215.74</v>
       </c>
       <c r="G93">
         <v>1.39</v>
@@ -8913,37 +8913,37 @@
         <v>20.4</v>
       </c>
       <c r="M93">
-        <v>50.318541</v>
+        <v>50.871492</v>
       </c>
       <c r="N93">
-        <v>-29.918541</v>
+        <v>-30.471492</v>
       </c>
       <c r="O93">
-        <v>-10.47148935</v>
+        <v>-10.6650222</v>
       </c>
       <c r="P93">
-        <v>-19.44705165000001</v>
+        <v>-19.8064698</v>
       </c>
       <c r="Q93">
-        <v>-16.54705165</v>
+        <v>-16.9064698</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.33187173024686</v>
+        <v>0.3676306965277175</v>
       </c>
       <c r="T93">
-        <v>5.23950420371322</v>
+        <v>5.894442229177374</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.141896006086504</v>
+        <v>0.1403536581942594</v>
       </c>
       <c r="W93">
-        <v>0.2023409217648024</v>
+        <v>0.2027046073977936</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4054171602471541</v>
+        <v>0.4010104519835982</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2158986945281876</v>
+        <v>0.2177986945281875</v>
       </c>
       <c r="C94">
-        <v>-155.6075743964406</v>
+        <v>-158.5345983099656</v>
       </c>
       <c r="D94">
-        <v>58.74242560355945</v>
+        <v>58.1604016900344</v>
       </c>
       <c r="E94">
-        <v>189.24</v>
+        <v>191.585</v>
       </c>
       <c r="F94">
-        <v>215.74</v>
+        <v>218.085</v>
       </c>
       <c r="G94">
         <v>1.39</v>
@@ -8995,37 +8995,37 @@
         <v>20.4</v>
       </c>
       <c r="M94">
-        <v>50.871492</v>
+        <v>51.424443</v>
       </c>
       <c r="N94">
-        <v>-30.471492</v>
+        <v>-31.02444300000001</v>
       </c>
       <c r="O94">
-        <v>-10.6650222</v>
+        <v>-10.85855505</v>
       </c>
       <c r="P94">
-        <v>-19.8064698</v>
+        <v>-20.16588795000001</v>
       </c>
       <c r="Q94">
-        <v>-16.9064698</v>
+        <v>-17.26588795</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3676306965277175</v>
+        <v>0.4136065103173915</v>
       </c>
       <c r="T94">
-        <v>5.894442229177374</v>
+        <v>6.736505404774142</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.1403536581942594</v>
+        <v>0.138844479073891</v>
       </c>
       <c r="W94">
-        <v>0.2027046073977936</v>
+        <v>0.2030604718343765</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4010104519835982</v>
+        <v>0.3966985116396885</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2177986945281875</v>
+        <v>0.2196986945281875</v>
       </c>
       <c r="C95">
-        <v>-158.5345983099656</v>
+        <v>-161.4502019123484</v>
       </c>
       <c r="D95">
-        <v>58.1604016900344</v>
+        <v>57.58979808765164</v>
       </c>
       <c r="E95">
-        <v>191.585</v>
+        <v>193.93</v>
       </c>
       <c r="F95">
-        <v>218.085</v>
+        <v>220.43</v>
       </c>
       <c r="G95">
         <v>1.39</v>
@@ -9077,37 +9077,37 @@
         <v>20.4</v>
       </c>
       <c r="M95">
-        <v>51.424443</v>
+        <v>51.977394</v>
       </c>
       <c r="N95">
-        <v>-31.02444300000001</v>
+        <v>-31.57739400000001</v>
       </c>
       <c r="O95">
-        <v>-10.85855505</v>
+        <v>-11.0520879</v>
       </c>
       <c r="P95">
-        <v>-20.16588795000001</v>
+        <v>-20.5253061</v>
       </c>
       <c r="Q95">
-        <v>-17.26588795</v>
+        <v>-17.6253061</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4136065103173915</v>
+        <v>0.4749075953702901</v>
       </c>
       <c r="T95">
-        <v>6.736505404774142</v>
+        <v>7.859256305569835</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.138844479073891</v>
+        <v>0.137367410147573</v>
       </c>
       <c r="W95">
-        <v>0.2030604718343765</v>
+        <v>0.2034087646872023</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3966985116396885</v>
+        <v>0.3924783147073514</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2196986945281875</v>
+        <v>0.2215986945281876</v>
       </c>
       <c r="C96">
-        <v>-161.4502019123484</v>
+        <v>-164.3547180671579</v>
       </c>
       <c r="D96">
-        <v>57.58979808765164</v>
+        <v>57.03028193284212</v>
       </c>
       <c r="E96">
-        <v>193.93</v>
+        <v>196.275</v>
       </c>
       <c r="F96">
-        <v>220.43</v>
+        <v>222.775</v>
       </c>
       <c r="G96">
         <v>1.39</v>
@@ -9159,37 +9159,37 @@
         <v>20.4</v>
       </c>
       <c r="M96">
-        <v>51.977394</v>
+        <v>52.530345</v>
       </c>
       <c r="N96">
-        <v>-31.57739400000001</v>
+        <v>-32.13034500000001</v>
       </c>
       <c r="O96">
-        <v>-11.0520879</v>
+        <v>-11.24562075</v>
       </c>
       <c r="P96">
-        <v>-20.5253061</v>
+        <v>-20.88472425</v>
       </c>
       <c r="Q96">
-        <v>-17.6253061</v>
+        <v>-17.98472425</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4749075953702901</v>
+        <v>0.5607291144443484</v>
       </c>
       <c r="T96">
-        <v>7.859256305569835</v>
+        <v>9.431107566683806</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.137367410147573</v>
+        <v>0.1359214374091775</v>
       </c>
       <c r="W96">
-        <v>0.2034087646872023</v>
+        <v>0.2037497250589159</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3924783147073514</v>
+        <v>0.3883469640262214</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2215986945281876</v>
+        <v>0.2234986945281876</v>
       </c>
       <c r="C97">
-        <v>-164.3547180671579</v>
+        <v>-167.248466826631</v>
       </c>
       <c r="D97">
-        <v>57.03028193284212</v>
+        <v>56.48153317336894</v>
       </c>
       <c r="E97">
-        <v>196.275</v>
+        <v>198.62</v>
       </c>
       <c r="F97">
-        <v>222.775</v>
+        <v>225.12</v>
       </c>
       <c r="G97">
         <v>1.39</v>
@@ -9241,37 +9241,37 @@
         <v>20.4</v>
       </c>
       <c r="M97">
-        <v>52.530345</v>
+        <v>53.083296</v>
       </c>
       <c r="N97">
-        <v>-32.13034500000001</v>
+        <v>-32.68329600000001</v>
       </c>
       <c r="O97">
-        <v>-11.24562075</v>
+        <v>-11.4391536</v>
       </c>
       <c r="P97">
-        <v>-20.88472425</v>
+        <v>-21.2441424</v>
       </c>
       <c r="Q97">
-        <v>-17.98472425</v>
+        <v>-18.3441424</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5607291144443484</v>
+        <v>0.6894613930554359</v>
       </c>
       <c r="T97">
-        <v>9.431107566683806</v>
+        <v>11.78888445835477</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1359214374091775</v>
+        <v>0.1345055891028319</v>
       </c>
       <c r="W97">
-        <v>0.2037497250589159</v>
+        <v>0.2040835820895523</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3883469640262214</v>
+        <v>0.3843016831509483</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2234986945281876</v>
+        <v>0.2253986945281875</v>
       </c>
       <c r="C98">
-        <v>-167.248466826631</v>
+        <v>-170.1317560421556</v>
       </c>
       <c r="D98">
-        <v>56.48153317336894</v>
+        <v>55.94324395784442</v>
       </c>
       <c r="E98">
-        <v>198.62</v>
+        <v>200.965</v>
       </c>
       <c r="F98">
-        <v>225.12</v>
+        <v>227.465</v>
       </c>
       <c r="G98">
         <v>1.39</v>
@@ -9323,37 +9323,37 @@
         <v>20.4</v>
       </c>
       <c r="M98">
-        <v>53.083296</v>
+        <v>53.636247</v>
       </c>
       <c r="N98">
-        <v>-32.68329600000001</v>
+        <v>-33.23624700000001</v>
       </c>
       <c r="O98">
-        <v>-11.4391536</v>
+        <v>-11.63268645</v>
       </c>
       <c r="P98">
-        <v>-21.2441424</v>
+        <v>-21.60356055</v>
       </c>
       <c r="Q98">
-        <v>-18.3441424</v>
+        <v>-18.70356055</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6894613930554341</v>
+        <v>0.9040151907405789</v>
       </c>
       <c r="T98">
-        <v>11.78888445835473</v>
+        <v>15.71851261113964</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1345055891028319</v>
+        <v>0.1331189335450707</v>
       </c>
       <c r="W98">
-        <v>0.2040835820895523</v>
+        <v>0.2044105554700723</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3843016831509483</v>
+        <v>0.3803398101287735</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2253986945281875</v>
+        <v>0.2272986945281876</v>
       </c>
       <c r="C99">
-        <v>-170.1317560421556</v>
+        <v>-173.0048819401737</v>
       </c>
       <c r="D99">
-        <v>55.94324395784442</v>
+        <v>55.41511805982634</v>
       </c>
       <c r="E99">
-        <v>200.965</v>
+        <v>203.31</v>
       </c>
       <c r="F99">
-        <v>227.465</v>
+        <v>229.81</v>
       </c>
       <c r="G99">
         <v>1.39</v>
@@ -9405,37 +9405,37 @@
         <v>20.4</v>
       </c>
       <c r="M99">
-        <v>53.636247</v>
+        <v>54.189198</v>
       </c>
       <c r="N99">
-        <v>-33.23624700000001</v>
+        <v>-33.78919800000001</v>
       </c>
       <c r="O99">
-        <v>-11.63268645</v>
+        <v>-11.8262193</v>
       </c>
       <c r="P99">
-        <v>-21.60356055</v>
+        <v>-21.9629787</v>
       </c>
       <c r="Q99">
-        <v>-18.70356055</v>
+        <v>-19.0629787</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9040151907405789</v>
+        <v>1.333122786110868</v>
       </c>
       <c r="T99">
-        <v>15.71851261113964</v>
+        <v>23.57776891670946</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1331189335450707</v>
+        <v>0.1317605770803251</v>
       </c>
       <c r="W99">
-        <v>0.2044105554700723</v>
+        <v>0.2047308559244594</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3803398101287735</v>
+        <v>0.3764587916580717</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2272986945281876</v>
+        <v>0.2291986945281875</v>
       </c>
       <c r="C100">
-        <v>-173.0048819401737</v>
+        <v>-175.8681296657702</v>
       </c>
       <c r="D100">
-        <v>55.41511805982634</v>
+        <v>54.89687033422977</v>
       </c>
       <c r="E100">
-        <v>203.31</v>
+        <v>205.655</v>
       </c>
       <c r="F100">
-        <v>229.81</v>
+        <v>232.155</v>
       </c>
       <c r="G100">
         <v>1.39</v>
@@ -9487,37 +9487,37 @@
         <v>20.4</v>
       </c>
       <c r="M100">
-        <v>54.189198</v>
+        <v>54.742149</v>
       </c>
       <c r="N100">
-        <v>-33.78919800000001</v>
+        <v>-34.34214900000001</v>
       </c>
       <c r="O100">
-        <v>-11.8262193</v>
+        <v>-12.01975215</v>
       </c>
       <c r="P100">
-        <v>-21.9629787</v>
+        <v>-22.32239685</v>
       </c>
       <c r="Q100">
-        <v>-19.0629787</v>
+        <v>-19.42239685</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.333122786110868</v>
+        <v>2.620445572221736</v>
       </c>
       <c r="T100">
-        <v>23.57776891670946</v>
+        <v>47.15553783341893</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1317605770803251</v>
+        <v>0.1304296621603218</v>
       </c>
       <c r="W100">
-        <v>0.2047308559244594</v>
+        <v>0.2050446856625961</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3764587916580717</v>
+        <v>0.3726561776009195</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2291986945281875</v>
-      </c>
-      <c r="C101">
-        <v>-175.8681296657702</v>
-      </c>
-      <c r="D101">
-        <v>54.89687033422977</v>
-      </c>
-      <c r="E101">
-        <v>205.655</v>
-      </c>
-      <c r="F101">
-        <v>232.155</v>
-      </c>
-      <c r="G101">
-        <v>1.39</v>
-      </c>
-      <c r="H101">
-        <v>208</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>23.3</v>
-      </c>
-      <c r="K101">
-        <v>2.900000000000002</v>
-      </c>
-      <c r="L101">
-        <v>20.4</v>
-      </c>
-      <c r="M101">
-        <v>54.742149</v>
-      </c>
-      <c r="N101">
-        <v>-34.34214900000001</v>
-      </c>
-      <c r="O101">
-        <v>-12.01975215</v>
-      </c>
-      <c r="P101">
-        <v>-22.32239685</v>
-      </c>
-      <c r="Q101">
-        <v>-19.42239685</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.620445572221736</v>
-      </c>
-      <c r="T101">
-        <v>47.15553783341893</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.1304296621603218</v>
-      </c>
-      <c r="W101">
-        <v>0.2050446856625961</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3726561776009195</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
